--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -477,7 +477,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
     </row>
@@ -504,7 +504,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
     </row>
@@ -531,7 +531,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
     </row>
@@ -558,7 +558,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
     </row>
@@ -585,7 +585,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
     </row>
@@ -612,7 +612,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2026-05-17</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -457,54 +457,54 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0939.HK</t>
+          <t>1810.HK</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>銀行</t>
+          <t>科技</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8.779999999999999</v>
+        <v>30.66</v>
       </c>
       <c r="D2" t="n">
-        <v>185720056</v>
+        <v>116609036</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.01</v>
+        <v>-0.13</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1810.HK</t>
+          <t>0939.HK</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>科技</t>
+          <t>銀行</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>30.7</v>
+        <v>8.76</v>
       </c>
       <c r="D3" t="n">
-        <v>152641980</v>
+        <v>107298258</v>
       </c>
       <c r="E3" t="n">
-        <v>-3.22</v>
+        <v>-0.23</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -520,72 +520,72 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>82.7</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>41139543</v>
+        <v>41368475</v>
       </c>
       <c r="E4" t="n">
-        <v>-3.5</v>
+        <v>-0.67</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0700.HK</t>
+          <t>1211.HK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>科技</t>
+          <t>新能源</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>456.4</v>
+        <v>93.8</v>
       </c>
       <c r="D5" t="n">
-        <v>26449868</v>
+        <v>29650908</v>
       </c>
       <c r="E5" t="n">
-        <v>0.33</v>
+        <v>-2.75</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1211.HK</t>
+          <t>0700.HK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>新能源</t>
+          <t>科技</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>96.45</v>
+        <v>449.2</v>
       </c>
       <c r="D6" t="n">
-        <v>21951647</v>
+        <v>29502376</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.73</v>
+        <v>-1.58</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>
@@ -601,18 +601,18 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>139.4</v>
+        <v>138.1</v>
       </c>
       <c r="D7" t="n">
-        <v>9189819</v>
+        <v>12750622</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.78</v>
+        <v>-0.93</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-05-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -465,15 +465,11 @@
           <t>科技</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>30.66</v>
-      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
         <v>116609036</v>
       </c>
-      <c r="E2" t="n">
-        <v>-0.13</v>
-      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
@@ -492,15 +488,11 @@
           <t>銀行</t>
         </is>
       </c>
-      <c r="C3" t="n">
-        <v>8.76</v>
-      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
         <v>107298258</v>
       </c>
-      <c r="E3" t="n">
-        <v>-0.23</v>
-      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
@@ -519,15 +511,11 @@
           <t>科技</t>
         </is>
       </c>
-      <c r="C4" t="n">
-        <v>82.15000000000001</v>
-      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
         <v>41368475</v>
       </c>
-      <c r="E4" t="n">
-        <v>-0.67</v>
-      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
@@ -546,15 +534,11 @@
           <t>新能源</t>
         </is>
       </c>
-      <c r="C5" t="n">
-        <v>93.8</v>
-      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
         <v>29650908</v>
       </c>
-      <c r="E5" t="n">
-        <v>-2.75</v>
-      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
@@ -573,15 +557,11 @@
           <t>科技</t>
         </is>
       </c>
-      <c r="C6" t="n">
-        <v>449.2</v>
-      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
         <v>29502376</v>
       </c>
-      <c r="E6" t="n">
-        <v>-1.58</v>
-      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
@@ -600,15 +580,11 @@
           <t>銀行</t>
         </is>
       </c>
-      <c r="C7" t="n">
-        <v>138.1</v>
-      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
         <v>12750622</v>
       </c>
-      <c r="E7" t="n">
-        <v>-0.93</v>
-      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,53 +457,61 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1810.HK</t>
+          <t>0939.HK</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>科技</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>8.859999999999999</v>
+      </c>
       <c r="D2" t="n">
-        <v>116609036</v>
-      </c>
-      <c r="E2" t="inlineStr"/>
+        <v>124665096</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1.14</v>
+      </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0939.HK</t>
+          <t>1810.HK</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>銀行</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>30.62</v>
+      </c>
       <c r="D3" t="n">
-        <v>107298258</v>
-      </c>
-      <c r="E3" t="inlineStr"/>
+        <v>63644141</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-0.13</v>
+      </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3690.HK</t>
+          <t>0700.HK</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -511,84 +519,73 @@
           <t>科技</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="n">
+        <v>462.2</v>
+      </c>
       <c r="D4" t="n">
-        <v>41368475</v>
-      </c>
-      <c r="E4" t="inlineStr"/>
+        <v>26592706</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2.89</v>
+      </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1211.HK</t>
+          <t>3690.HK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>新能源</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>83.34999999999999</v>
+      </c>
       <c r="D5" t="n">
-        <v>29650908</v>
-      </c>
-      <c r="E5" t="inlineStr"/>
+        <v>20209776</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1.46</v>
+      </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0700.HK</t>
+          <t>1211.HK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>科技</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>94.5</v>
+      </c>
       <c r="D6" t="n">
-        <v>29502376</v>
-      </c>
-      <c r="E6" t="inlineStr"/>
+        <v>13670333</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.75</v>
+      </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>0005.HK</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>銀行</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="n">
-        <v>12750622</v>
-      </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
     </row>
@@ -645,7 +642,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -465,15 +465,11 @@
           <t>銀行</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>8.859999999999999</v>
-      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>124665096</v>
-      </c>
-      <c r="E2" t="n">
-        <v>1.14</v>
-      </c>
+        <v>192341775</v>
+      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
@@ -492,15 +488,11 @@
           <t>科技</t>
         </is>
       </c>
-      <c r="C3" t="n">
-        <v>30.62</v>
-      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>63644141</v>
-      </c>
-      <c r="E3" t="n">
-        <v>-0.13</v>
-      </c>
+        <v>89701722</v>
+      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
@@ -519,15 +511,11 @@
           <t>科技</t>
         </is>
       </c>
-      <c r="C4" t="n">
-        <v>462.2</v>
-      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>26592706</v>
-      </c>
-      <c r="E4" t="n">
-        <v>2.89</v>
-      </c>
+        <v>33738701</v>
+      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
@@ -546,15 +534,11 @@
           <t>科技</t>
         </is>
       </c>
-      <c r="C5" t="n">
-        <v>83.34999999999999</v>
-      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>20209776</v>
-      </c>
-      <c r="E5" t="n">
-        <v>1.46</v>
-      </c>
+        <v>30810678</v>
+      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
@@ -573,17 +557,36 @@
           <t>新能源</t>
         </is>
       </c>
-      <c r="C6" t="n">
-        <v>94.5</v>
-      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>13670333</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0.75</v>
-      </c>
+        <v>18431512</v>
+      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>0005.HK</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="n">
+        <v>12111898</v>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
@@ -642,7 +645,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -465,15 +465,19 @@
           <t>銀行</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="n">
+        <v>8.73</v>
+      </c>
       <c r="D2" t="n">
-        <v>192341775</v>
-      </c>
-      <c r="E2" t="inlineStr"/>
+        <v>176292806</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-1.36</v>
+      </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
     </row>
@@ -488,38 +492,46 @@
           <t>科技</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="n">
+        <v>30.14</v>
+      </c>
       <c r="D3" t="n">
-        <v>89701722</v>
-      </c>
-      <c r="E3" t="inlineStr"/>
+        <v>109868643</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-1.63</v>
+      </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0700.HK</t>
+          <t>1211.HK</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>科技</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>90.2</v>
+      </c>
       <c r="D4" t="n">
-        <v>33738701</v>
-      </c>
-      <c r="E4" t="inlineStr"/>
+        <v>34280540</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-3.94</v>
+      </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
     </row>
@@ -534,38 +546,46 @@
           <t>科技</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="n">
+        <v>82.84999999999999</v>
+      </c>
       <c r="D5" t="n">
-        <v>30810678</v>
-      </c>
-      <c r="E5" t="inlineStr"/>
+        <v>25163892</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-0.24</v>
+      </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1211.HK</t>
+          <t>0700.HK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>新能源</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>455.2</v>
+      </c>
       <c r="D6" t="n">
-        <v>18431512</v>
-      </c>
-      <c r="E6" t="inlineStr"/>
+        <v>18927606</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-1.04</v>
+      </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
     </row>
@@ -580,15 +600,19 @@
           <t>銀行</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="n">
+        <v>138.7</v>
+      </c>
       <c r="D7" t="n">
-        <v>12111898</v>
-      </c>
-      <c r="E7" t="inlineStr"/>
+        <v>7692378</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-1.14</v>
+      </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -465,19 +465,15 @@
           <t>銀行</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>8.73</v>
-      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>176292806</v>
-      </c>
-      <c r="E2" t="n">
-        <v>-1.36</v>
-      </c>
+        <v>188026592</v>
+      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
     </row>
@@ -492,53 +488,45 @@
           <t>科技</t>
         </is>
       </c>
-      <c r="C3" t="n">
-        <v>30.14</v>
-      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>109868643</v>
-      </c>
-      <c r="E3" t="n">
-        <v>-1.63</v>
-      </c>
+        <v>117068449</v>
+      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1211.HK</t>
+          <t>3690.HK</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>新能源</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>90.2</v>
-      </c>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>34280540</v>
-      </c>
-      <c r="E4" t="n">
-        <v>-3.94</v>
-      </c>
+        <v>45119186</v>
+      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3690.HK</t>
+          <t>0700.HK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -546,46 +534,38 @@
           <t>科技</t>
         </is>
       </c>
-      <c r="C5" t="n">
-        <v>82.84999999999999</v>
-      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>25163892</v>
-      </c>
-      <c r="E5" t="n">
-        <v>-0.24</v>
-      </c>
+        <v>39654395</v>
+      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0700.HK</t>
+          <t>1211.HK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>科技</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>455.2</v>
-      </c>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>18927606</v>
-      </c>
-      <c r="E6" t="n">
-        <v>-1.04</v>
-      </c>
+        <v>21982614</v>
+      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
     </row>
@@ -600,19 +580,15 @@
           <t>銀行</t>
         </is>
       </c>
-      <c r="C7" t="n">
-        <v>138.7</v>
-      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>7692378</v>
-      </c>
-      <c r="E7" t="n">
-        <v>-1.14</v>
-      </c>
+        <v>16983186</v>
+      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -467,13 +467,13 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>188026592</v>
+        <v>196298555</v>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
     </row>
@@ -490,13 +490,13 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>117068449</v>
+        <v>100972558</v>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
     </row>
@@ -513,13 +513,13 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>45119186</v>
+        <v>39787270</v>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
     </row>
@@ -536,59 +536,59 @@
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>39654395</v>
+        <v>23999519</v>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1211.HK</t>
+          <t>0005.HK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>新能源</t>
+          <t>銀行</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>21982614</v>
+        <v>18583483</v>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0005.HK</t>
+          <t>1211.HK</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>銀行</t>
+          <t>新能源</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>16983186</v>
+        <v>18267433</v>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -465,15 +465,19 @@
           <t>銀行</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="n">
+        <v>8.77</v>
+      </c>
       <c r="D2" t="n">
-        <v>196298555</v>
-      </c>
-      <c r="E2" t="inlineStr"/>
+        <v>196195555</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.92</v>
+      </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
     </row>
@@ -488,15 +492,19 @@
           <t>科技</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="n">
+        <v>30</v>
+      </c>
       <c r="D3" t="n">
-        <v>100972558</v>
-      </c>
-      <c r="E3" t="inlineStr"/>
+        <v>100960958</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1.15</v>
+      </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
     </row>
@@ -511,15 +519,19 @@
           <t>科技</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="n">
+        <v>81.34999999999999</v>
+      </c>
       <c r="D4" t="n">
-        <v>39787270</v>
-      </c>
-      <c r="E4" t="inlineStr"/>
+        <v>39784370</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-0.91</v>
+      </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
     </row>
@@ -534,15 +546,19 @@
           <t>科技</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="n">
+        <v>441.4</v>
+      </c>
       <c r="D5" t="n">
-        <v>23999519</v>
-      </c>
-      <c r="E5" t="inlineStr"/>
+        <v>23998219</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.55</v>
+      </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
     </row>
@@ -557,15 +573,19 @@
           <t>銀行</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="n">
+        <v>143.9</v>
+      </c>
       <c r="D6" t="n">
-        <v>18583483</v>
-      </c>
-      <c r="E6" t="inlineStr"/>
+        <v>18580283</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1.55</v>
+      </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
     </row>
@@ -580,15 +600,19 @@
           <t>新能源</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="n">
+        <v>91.59999999999999</v>
+      </c>
       <c r="D7" t="n">
-        <v>18267433</v>
-      </c>
-      <c r="E7" t="inlineStr"/>
+        <v>18267233</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1.16</v>
+      </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -477,7 +477,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-24</t>
         </is>
       </c>
     </row>
@@ -504,7 +504,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-24</t>
         </is>
       </c>
     </row>
@@ -531,7 +531,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-24</t>
         </is>
       </c>
     </row>
@@ -558,7 +558,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-24</t>
         </is>
       </c>
     </row>
@@ -585,7 +585,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-24</t>
         </is>
       </c>
     </row>
@@ -612,7 +612,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-24</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -477,7 +477,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -504,7 +504,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -531,7 +531,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -558,7 +558,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -585,7 +585,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -612,7 +612,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -466,18 +466,18 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8.77</v>
+        <v>8.73</v>
       </c>
       <c r="D2" t="n">
-        <v>196195555</v>
+        <v>253253893</v>
       </c>
       <c r="E2" t="n">
-        <v>0.92</v>
+        <v>-0.46</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
     </row>
@@ -493,18 +493,18 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>30</v>
+        <v>29.76</v>
       </c>
       <c r="D3" t="n">
-        <v>100960958</v>
+        <v>148283733</v>
       </c>
       <c r="E3" t="n">
-        <v>1.15</v>
+        <v>-0.8</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
     </row>
@@ -520,18 +520,18 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>81.34999999999999</v>
+        <v>78.8</v>
       </c>
       <c r="D4" t="n">
-        <v>39784370</v>
+        <v>67357066</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.91</v>
+        <v>-3.13</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
     </row>
@@ -547,72 +547,72 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>441.4</v>
+        <v>439</v>
       </c>
       <c r="D5" t="n">
-        <v>23998219</v>
+        <v>32795639</v>
       </c>
       <c r="E5" t="n">
-        <v>0.55</v>
+        <v>-0.54</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0005.HK</t>
+          <t>1211.HK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>銀行</t>
+          <t>新能源</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>143.9</v>
+        <v>93.65000000000001</v>
       </c>
       <c r="D6" t="n">
-        <v>18580283</v>
+        <v>32533024</v>
       </c>
       <c r="E6" t="n">
-        <v>1.55</v>
+        <v>2.24</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1211.HK</t>
+          <t>0005.HK</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>新能源</t>
+          <t>銀行</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>91.59999999999999</v>
+        <v>145.5</v>
       </c>
       <c r="D7" t="n">
-        <v>18267233</v>
+        <v>19646590</v>
       </c>
       <c r="E7" t="n">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -457,54 +457,54 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0939.HK</t>
+          <t>1810.HK</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>銀行</t>
+          <t>科技</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8.73</v>
+        <v>28.4</v>
       </c>
       <c r="D2" t="n">
-        <v>253253893</v>
+        <v>283417486</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.46</v>
+        <v>-4.57</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1810.HK</t>
+          <t>0939.HK</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>科技</t>
+          <t>銀行</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>29.76</v>
+        <v>8.58</v>
       </c>
       <c r="D3" t="n">
-        <v>148283733</v>
+        <v>246730455</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.8</v>
+        <v>-1.72</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
     </row>
@@ -520,72 +520,72 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>78.8</v>
+        <v>77.7</v>
       </c>
       <c r="D4" t="n">
-        <v>67357066</v>
+        <v>34078568</v>
       </c>
       <c r="E4" t="n">
-        <v>-3.13</v>
+        <v>-1.4</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0700.HK</t>
+          <t>1211.HK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>科技</t>
+          <t>新能源</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>439</v>
+        <v>90.7</v>
       </c>
       <c r="D5" t="n">
-        <v>32795639</v>
+        <v>32965656</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.54</v>
+        <v>-3.15</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1211.HK</t>
+          <t>0700.HK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>新能源</t>
+          <t>科技</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>93.65000000000001</v>
+        <v>434.4</v>
       </c>
       <c r="D6" t="n">
-        <v>32533024</v>
+        <v>24863984</v>
       </c>
       <c r="E6" t="n">
-        <v>2.24</v>
+        <v>-1.05</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
     </row>
@@ -601,18 +601,18 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>145.5</v>
+        <v>146.6</v>
       </c>
       <c r="D7" t="n">
-        <v>19646590</v>
+        <v>14520391</v>
       </c>
       <c r="E7" t="n">
-        <v>1.11</v>
+        <v>0.76</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -457,54 +457,54 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1810.HK</t>
+          <t>0939.HK</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>科技</t>
+          <t>銀行</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>28.4</v>
+        <v>8.48</v>
       </c>
       <c r="D2" t="n">
-        <v>283417486</v>
+        <v>319921929</v>
       </c>
       <c r="E2" t="n">
-        <v>-4.57</v>
+        <v>-1.17</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0939.HK</t>
+          <t>1810.HK</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>銀行</t>
+          <t>科技</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>8.58</v>
+        <v>28.56</v>
       </c>
       <c r="D3" t="n">
-        <v>246730455</v>
+        <v>238003859</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.72</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
     </row>
@@ -520,72 +520,72 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>77.7</v>
+        <v>73.3</v>
       </c>
       <c r="D4" t="n">
-        <v>34078568</v>
+        <v>94713412</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.4</v>
+        <v>-5.66</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1211.HK</t>
+          <t>0700.HK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>新能源</t>
+          <t>科技</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>90.7</v>
+        <v>425</v>
       </c>
       <c r="D5" t="n">
-        <v>32965656</v>
+        <v>42196103</v>
       </c>
       <c r="E5" t="n">
-        <v>-3.15</v>
+        <v>-2.16</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0700.HK</t>
+          <t>1211.HK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>科技</t>
+          <t>新能源</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>434.4</v>
+        <v>90.3</v>
       </c>
       <c r="D6" t="n">
-        <v>24863984</v>
+        <v>30571211</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.05</v>
+        <v>-0.44</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
     </row>
@@ -601,18 +601,18 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>146.6</v>
+        <v>145.3</v>
       </c>
       <c r="D7" t="n">
-        <v>14520391</v>
+        <v>17372582</v>
       </c>
       <c r="E7" t="n">
-        <v>0.76</v>
+        <v>-0.89</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-05-28</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -466,18 +466,18 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8.48</v>
+        <v>8.49</v>
       </c>
       <c r="D2" t="n">
-        <v>319921929</v>
+        <v>1230798186</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.17</v>
+        <v>0.12</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
     </row>
@@ -493,18 +493,18 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>28.56</v>
+        <v>28.04</v>
       </c>
       <c r="D3" t="n">
-        <v>238003859</v>
+        <v>248812612</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5600000000000001</v>
+        <v>-1.82</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
     </row>
@@ -520,72 +520,72 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>73.3</v>
+        <v>73.45</v>
       </c>
       <c r="D4" t="n">
-        <v>94713412</v>
+        <v>81724196</v>
       </c>
       <c r="E4" t="n">
-        <v>-5.66</v>
+        <v>0.2</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0700.HK</t>
+          <t>1211.HK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>科技</t>
+          <t>新能源</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>425</v>
+        <v>91.3</v>
       </c>
       <c r="D5" t="n">
-        <v>42196103</v>
+        <v>50503512</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.16</v>
+        <v>1.11</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1211.HK</t>
+          <t>0700.HK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>新能源</t>
+          <t>科技</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>90.3</v>
+        <v>427.2</v>
       </c>
       <c r="D6" t="n">
-        <v>30571211</v>
+        <v>48005475</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.44</v>
+        <v>0.52</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
     </row>
@@ -601,18 +601,18 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>145.3</v>
+        <v>145.1</v>
       </c>
       <c r="D7" t="n">
-        <v>17372582</v>
+        <v>13019970</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.89</v>
+        <v>-0.14</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -477,7 +477,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
     </row>
@@ -504,7 +504,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
     </row>
@@ -531,7 +531,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
     </row>
@@ -558,7 +558,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
     </row>
@@ -585,7 +585,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
     </row>
@@ -612,7 +612,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-30</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -477,7 +477,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-31</t>
         </is>
       </c>
     </row>
@@ -504,7 +504,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-31</t>
         </is>
       </c>
     </row>
@@ -531,7 +531,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-31</t>
         </is>
       </c>
     </row>
@@ -558,7 +558,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-31</t>
         </is>
       </c>
     </row>
@@ -585,7 +585,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-31</t>
         </is>
       </c>
     </row>
@@ -612,7 +612,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
+          <t>2026-05-31</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -466,18 +466,18 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8.49</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>1230798186</v>
+        <v>350866907</v>
       </c>
       <c r="E2" t="n">
-        <v>0.12</v>
+        <v>0.47</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -493,18 +493,18 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>28.04</v>
+        <v>28.72</v>
       </c>
       <c r="D3" t="n">
-        <v>248812612</v>
+        <v>164616523</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.82</v>
+        <v>2.43</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -520,72 +520,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>73.45</v>
+        <v>78.25</v>
       </c>
       <c r="D4" t="n">
-        <v>81724196</v>
+        <v>72625452</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F4" t="inlineStr"/>
+        <v>6.54</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>🔥爆升</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1211.HK</t>
+          <t>0700.HK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>新能源</t>
+          <t>科技</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>91.3</v>
+        <v>436</v>
       </c>
       <c r="D5" t="n">
-        <v>50503512</v>
+        <v>35164391</v>
       </c>
       <c r="E5" t="n">
-        <v>1.11</v>
+        <v>2.06</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0700.HK</t>
+          <t>1211.HK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>科技</t>
+          <t>新能源</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>427.2</v>
+        <v>90.75</v>
       </c>
       <c r="D6" t="n">
-        <v>48005475</v>
+        <v>24241377</v>
       </c>
       <c r="E6" t="n">
-        <v>0.52</v>
+        <v>-0.6</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>
@@ -601,18 +605,18 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>145.1</v>
+        <v>146.3</v>
       </c>
       <c r="D7" t="n">
-        <v>13019970</v>
+        <v>11125038</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.14</v>
+        <v>0.83</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -466,18 +466,18 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8.529999999999999</v>
+        <v>8.66</v>
       </c>
       <c r="D2" t="n">
-        <v>350866907</v>
+        <v>202874745</v>
       </c>
       <c r="E2" t="n">
-        <v>0.47</v>
+        <v>1.52</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
     </row>
@@ -493,18 +493,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>28.72</v>
+        <v>29.62</v>
       </c>
       <c r="D3" t="n">
-        <v>164616523</v>
+        <v>178513477</v>
       </c>
       <c r="E3" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="F3" t="inlineStr"/>
+        <v>3.13</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>🔥爆升</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
     </row>
@@ -520,13 +524,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>78.25</v>
+        <v>85.5</v>
       </c>
       <c r="D4" t="n">
-        <v>72625452</v>
+        <v>136662320</v>
       </c>
       <c r="E4" t="n">
-        <v>6.54</v>
+        <v>9.27</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -535,7 +539,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
     </row>
@@ -551,18 +555,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>436</v>
+        <v>481.6</v>
       </c>
       <c r="D5" t="n">
-        <v>35164391</v>
+        <v>101874275</v>
       </c>
       <c r="E5" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="F5" t="inlineStr"/>
+        <v>10.46</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>🔥爆升</t>
+        </is>
+      </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
     </row>
@@ -578,18 +586,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>90.75</v>
+        <v>96.75</v>
       </c>
       <c r="D6" t="n">
-        <v>24241377</v>
+        <v>44730548</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="F6" t="inlineStr"/>
+        <v>6.61</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>🔥爆升</t>
+        </is>
+      </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
     </row>
@@ -605,18 +617,18 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>146.3</v>
+        <v>147.2</v>
       </c>
       <c r="D7" t="n">
-        <v>11125038</v>
+        <v>17445189</v>
       </c>
       <c r="E7" t="n">
-        <v>0.83</v>
+        <v>0.62</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -466,18 +466,18 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8.66</v>
+        <v>8.57</v>
       </c>
       <c r="D2" t="n">
-        <v>202874745</v>
+        <v>173013055</v>
       </c>
       <c r="E2" t="n">
-        <v>1.52</v>
+        <v>-1.04</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
     </row>
@@ -493,22 +493,18 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>29.62</v>
+        <v>28.58</v>
       </c>
       <c r="D3" t="n">
-        <v>178513477</v>
+        <v>142370227</v>
       </c>
       <c r="E3" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>🔥爆升</t>
-        </is>
-      </c>
+        <v>-3.51</v>
+      </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
     </row>
@@ -524,22 +520,18 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>85.5</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>136662320</v>
+        <v>83942077</v>
       </c>
       <c r="E4" t="n">
-        <v>9.27</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>🔥爆升</t>
-        </is>
-      </c>
+        <v>-5.96</v>
+      </c>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
     </row>
@@ -555,22 +547,18 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>481.6</v>
+        <v>466.4</v>
       </c>
       <c r="D5" t="n">
-        <v>101874275</v>
+        <v>49104320</v>
       </c>
       <c r="E5" t="n">
-        <v>10.46</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>🔥爆升</t>
-        </is>
-      </c>
+        <v>-3.16</v>
+      </c>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
     </row>
@@ -586,22 +574,18 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>96.75</v>
+        <v>93.25</v>
       </c>
       <c r="D6" t="n">
-        <v>44730548</v>
+        <v>28148039</v>
       </c>
       <c r="E6" t="n">
-        <v>6.61</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>🔥爆升</t>
-        </is>
-      </c>
+        <v>-3.62</v>
+      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
     </row>
@@ -617,18 +601,18 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>147.2</v>
+        <v>146.9</v>
       </c>
       <c r="D7" t="n">
-        <v>17445189</v>
+        <v>13176862</v>
       </c>
       <c r="E7" t="n">
-        <v>0.62</v>
+        <v>-0.2</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-03</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -466,18 +466,18 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8.57</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>173013055</v>
+        <v>172993390</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.04</v>
+        <v>-0.23</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
     </row>
@@ -493,18 +493,18 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>28.58</v>
+        <v>28.38</v>
       </c>
       <c r="D3" t="n">
-        <v>142370227</v>
+        <v>88262656</v>
       </c>
       <c r="E3" t="n">
-        <v>-3.51</v>
+        <v>-0.7</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
     </row>
@@ -520,18 +520,18 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>80.40000000000001</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="D4" t="n">
-        <v>83942077</v>
+        <v>43047835</v>
       </c>
       <c r="E4" t="n">
-        <v>-5.96</v>
+        <v>-2.24</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
     </row>
@@ -547,18 +547,18 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>466.4</v>
+        <v>459</v>
       </c>
       <c r="D5" t="n">
-        <v>49104320</v>
+        <v>29053909</v>
       </c>
       <c r="E5" t="n">
-        <v>-3.16</v>
+        <v>-1.59</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
     </row>
@@ -574,18 +574,18 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>93.25</v>
+        <v>91.8</v>
       </c>
       <c r="D6" t="n">
-        <v>28148039</v>
+        <v>24773902</v>
       </c>
       <c r="E6" t="n">
-        <v>-3.62</v>
+        <v>-1.55</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
     </row>
@@ -601,18 +601,18 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>146.9</v>
+        <v>146.4</v>
       </c>
       <c r="D7" t="n">
-        <v>13176862</v>
+        <v>11968429</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.2</v>
+        <v>-0.34</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -465,19 +465,15 @@
           <t>銀行</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>8.550000000000001</v>
-      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>172993390</v>
-      </c>
-      <c r="E2" t="n">
-        <v>-0.23</v>
-      </c>
+        <v>219025562</v>
+      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
     </row>
@@ -492,19 +488,15 @@
           <t>科技</t>
         </is>
       </c>
-      <c r="C3" t="n">
-        <v>28.38</v>
-      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>88262656</v>
-      </c>
-      <c r="E3" t="n">
-        <v>-0.7</v>
-      </c>
+        <v>154077195</v>
+      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
     </row>
@@ -519,19 +511,15 @@
           <t>科技</t>
         </is>
       </c>
-      <c r="C4" t="n">
-        <v>78.59999999999999</v>
-      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>43047835</v>
-      </c>
-      <c r="E4" t="n">
-        <v>-2.24</v>
-      </c>
+        <v>57510319</v>
+      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
     </row>
@@ -546,73 +534,61 @@
           <t>科技</t>
         </is>
       </c>
-      <c r="C5" t="n">
-        <v>459</v>
-      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>29053909</v>
-      </c>
-      <c r="E5" t="n">
-        <v>-1.59</v>
-      </c>
+        <v>31649780</v>
+      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1211.HK</t>
+          <t>0005.HK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>新能源</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>91.8</v>
-      </c>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>24773902</v>
-      </c>
-      <c r="E6" t="n">
-        <v>-1.55</v>
-      </c>
+        <v>29293119</v>
+      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0005.HK</t>
+          <t>1211.HK</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>銀行</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>146.4</v>
-      </c>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>11968429</v>
-      </c>
-      <c r="E7" t="n">
-        <v>-0.34</v>
-      </c>
+        <v>26158535</v>
+      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -465,15 +465,19 @@
           <t>銀行</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="n">
+        <v>8.720000000000001</v>
+      </c>
       <c r="D2" t="n">
-        <v>219025562</v>
-      </c>
-      <c r="E2" t="inlineStr"/>
+        <v>219022562</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1.99</v>
+      </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
@@ -488,15 +492,19 @@
           <t>科技</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="n">
+        <v>27.8</v>
+      </c>
       <c r="D3" t="n">
-        <v>154077195</v>
-      </c>
-      <c r="E3" t="inlineStr"/>
+        <v>154054795</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-2.04</v>
+      </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
@@ -511,15 +519,19 @@
           <t>科技</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="n">
+        <v>79.95</v>
+      </c>
       <c r="D4" t="n">
-        <v>57510319</v>
-      </c>
-      <c r="E4" t="inlineStr"/>
+        <v>57489919</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1.72</v>
+      </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
@@ -534,15 +546,19 @@
           <t>科技</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="n">
+        <v>453.2</v>
+      </c>
       <c r="D5" t="n">
         <v>31649780</v>
       </c>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="n">
+        <v>-1.26</v>
+      </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
@@ -557,15 +573,19 @@
           <t>銀行</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="n">
+        <v>141.8</v>
+      </c>
       <c r="D6" t="n">
         <v>29293119</v>
       </c>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="n">
+        <v>-3.14</v>
+      </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>
@@ -580,15 +600,19 @@
           <t>新能源</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="n">
+        <v>89.7</v>
+      </c>
       <c r="D7" t="n">
-        <v>26158535</v>
-      </c>
-      <c r="E7" t="inlineStr"/>
+        <v>26150935</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-2.29</v>
+      </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-06</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -477,7 +477,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-07</t>
         </is>
       </c>
     </row>
@@ -504,7 +504,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-07</t>
         </is>
       </c>
     </row>
@@ -531,7 +531,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-07</t>
         </is>
       </c>
     </row>
@@ -558,7 +558,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-07</t>
         </is>
       </c>
     </row>
@@ -585,7 +585,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-07</t>
         </is>
       </c>
     </row>
@@ -612,7 +612,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-07</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -466,18 +466,18 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8.720000000000001</v>
+        <v>8.76</v>
       </c>
       <c r="D2" t="n">
-        <v>219022562</v>
+        <v>249094895</v>
       </c>
       <c r="E2" t="n">
-        <v>1.99</v>
+        <v>0.46</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -493,18 +493,18 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>27.8</v>
+        <v>27.38</v>
       </c>
       <c r="D3" t="n">
-        <v>154054795</v>
+        <v>152036878</v>
       </c>
       <c r="E3" t="n">
-        <v>-2.04</v>
+        <v>-1.51</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -520,18 +520,18 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>79.95</v>
+        <v>76.25</v>
       </c>
       <c r="D4" t="n">
-        <v>57489919</v>
+        <v>63060620</v>
       </c>
       <c r="E4" t="n">
-        <v>1.72</v>
+        <v>-4.63</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
@@ -547,72 +547,72 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>453.2</v>
+        <v>446.4</v>
       </c>
       <c r="D5" t="n">
-        <v>31649780</v>
+        <v>29019096</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.26</v>
+        <v>-1.5</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0005.HK</t>
+          <t>1211.HK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>銀行</t>
+          <t>新能源</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>141.8</v>
+        <v>88.05</v>
       </c>
       <c r="D6" t="n">
-        <v>29293119</v>
+        <v>25945048</v>
       </c>
       <c r="E6" t="n">
-        <v>-3.14</v>
+        <v>-1.84</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1211.HK</t>
+          <t>0005.HK</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>新能源</t>
+          <t>銀行</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>89.7</v>
+        <v>142.3</v>
       </c>
       <c r="D7" t="n">
-        <v>26150935</v>
+        <v>15193347</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.29</v>
+        <v>0.35</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-08</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -465,19 +465,15 @@
           <t>銀行</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>8.76</v>
-      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>249094895</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.46</v>
-      </c>
+        <v>246117414</v>
+      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
     </row>
@@ -492,26 +488,22 @@
           <t>科技</t>
         </is>
       </c>
-      <c r="C3" t="n">
-        <v>27.38</v>
-      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>152036878</v>
-      </c>
-      <c r="E3" t="n">
-        <v>-1.51</v>
-      </c>
+        <v>103973917</v>
+      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3690.HK</t>
+          <t>0700.HK</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -519,26 +511,22 @@
           <t>科技</t>
         </is>
       </c>
-      <c r="C4" t="n">
-        <v>76.25</v>
-      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>63060620</v>
-      </c>
-      <c r="E4" t="n">
-        <v>-4.63</v>
-      </c>
+        <v>37388999</v>
+      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0700.HK</t>
+          <t>3690.HK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -546,19 +534,15 @@
           <t>科技</t>
         </is>
       </c>
-      <c r="C5" t="n">
-        <v>446.4</v>
-      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>29019096</v>
-      </c>
-      <c r="E5" t="n">
-        <v>-1.5</v>
-      </c>
+        <v>34274279</v>
+      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
     </row>
@@ -573,19 +557,15 @@
           <t>新能源</t>
         </is>
       </c>
-      <c r="C6" t="n">
-        <v>88.05</v>
-      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>25945048</v>
-      </c>
-      <c r="E6" t="n">
-        <v>-1.84</v>
-      </c>
+        <v>14799866</v>
+      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
     </row>
@@ -600,19 +580,15 @@
           <t>銀行</t>
         </is>
       </c>
-      <c r="C7" t="n">
-        <v>142.3</v>
-      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>15193347</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0.35</v>
-      </c>
+        <v>11631298</v>
+      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -465,15 +465,19 @@
           <t>銀行</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="n">
+        <v>8.75</v>
+      </c>
       <c r="D2" t="n">
-        <v>246117414</v>
-      </c>
-      <c r="E2" t="inlineStr"/>
+        <v>239320135</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.6899999999999999</v>
+      </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
     </row>
@@ -488,22 +492,26 @@
           <t>科技</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="n">
+        <v>26.32</v>
+      </c>
       <c r="D3" t="n">
-        <v>103973917</v>
-      </c>
-      <c r="E3" t="inlineStr"/>
+        <v>226252092</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-3.24</v>
+      </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0700.HK</t>
+          <t>3690.HK</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -511,22 +519,26 @@
           <t>科技</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="n">
+        <v>79</v>
+      </c>
       <c r="D4" t="n">
-        <v>37388999</v>
-      </c>
-      <c r="E4" t="inlineStr"/>
+        <v>56328337</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2.33</v>
+      </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3690.HK</t>
+          <t>0700.HK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -534,61 +546,73 @@
           <t>科技</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="n">
+        <v>465.6</v>
+      </c>
       <c r="D5" t="n">
-        <v>34274279</v>
-      </c>
-      <c r="E5" t="inlineStr"/>
+        <v>35788237</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2.74</v>
+      </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1211.HK</t>
+          <t>0005.HK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>新能源</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>135.3</v>
+      </c>
       <c r="D6" t="n">
-        <v>14799866</v>
-      </c>
-      <c r="E6" t="inlineStr"/>
+        <v>35400697</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-4.79</v>
+      </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0005.HK</t>
+          <t>1211.HK</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>銀行</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>86.19</v>
+      </c>
       <c r="D7" t="n">
-        <v>11631298</v>
-      </c>
-      <c r="E7" t="inlineStr"/>
+        <v>33622524</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-2.04</v>
+      </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-10</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -466,18 +466,18 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8.75</v>
+        <v>8.69</v>
       </c>
       <c r="D2" t="n">
-        <v>239320135</v>
+        <v>205357363</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6899999999999999</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
     </row>
@@ -493,18 +493,18 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>26.32</v>
+        <v>25.84</v>
       </c>
       <c r="D3" t="n">
-        <v>226252092</v>
+        <v>124356371</v>
       </c>
       <c r="E3" t="n">
-        <v>-3.24</v>
+        <v>-1.82</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
     </row>
@@ -520,18 +520,18 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>79</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="D4" t="n">
-        <v>56328337</v>
+        <v>34922354</v>
       </c>
       <c r="E4" t="n">
-        <v>2.33</v>
+        <v>-1.14</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
     </row>
@@ -547,72 +547,72 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>465.6</v>
+        <v>457.2</v>
       </c>
       <c r="D5" t="n">
-        <v>35788237</v>
+        <v>28580619</v>
       </c>
       <c r="E5" t="n">
-        <v>2.74</v>
+        <v>-1.8</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0005.HK</t>
+          <t>1211.HK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>銀行</t>
+          <t>新能源</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>135.3</v>
+        <v>84.95</v>
       </c>
       <c r="D6" t="n">
-        <v>35400697</v>
+        <v>20844023</v>
       </c>
       <c r="E6" t="n">
-        <v>-4.79</v>
+        <v>-1.44</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1211.HK</t>
+          <t>0005.HK</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>新能源</t>
+          <t>銀行</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>86.19</v>
+        <v>138.5</v>
       </c>
       <c r="D7" t="n">
-        <v>33622524</v>
+        <v>17746424</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.04</v>
+        <v>2.37</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-11</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -465,19 +465,15 @@
           <t>銀行</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>8.69</v>
-      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>205357363</v>
-      </c>
-      <c r="E2" t="n">
-        <v>-0.6899999999999999</v>
-      </c>
+        <v>248112067</v>
+      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
     </row>
@@ -492,19 +488,15 @@
           <t>科技</t>
         </is>
       </c>
-      <c r="C3" t="n">
-        <v>25.84</v>
-      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>124356371</v>
-      </c>
-      <c r="E3" t="n">
-        <v>-1.82</v>
-      </c>
+        <v>131885183</v>
+      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
     </row>
@@ -519,19 +511,15 @@
           <t>科技</t>
         </is>
       </c>
-      <c r="C4" t="n">
-        <v>78.09999999999999</v>
-      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>34922354</v>
-      </c>
-      <c r="E4" t="n">
-        <v>-1.14</v>
-      </c>
+        <v>47409244</v>
+      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
     </row>
@@ -546,19 +534,15 @@
           <t>科技</t>
         </is>
       </c>
-      <c r="C5" t="n">
-        <v>457.2</v>
-      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>28580619</v>
-      </c>
-      <c r="E5" t="n">
-        <v>-1.8</v>
-      </c>
+        <v>22348046</v>
+      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
     </row>
@@ -573,19 +557,15 @@
           <t>新能源</t>
         </is>
       </c>
-      <c r="C6" t="n">
-        <v>84.95</v>
-      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>20844023</v>
-      </c>
-      <c r="E6" t="n">
-        <v>-1.44</v>
-      </c>
+        <v>16499792</v>
+      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
     </row>
@@ -600,19 +580,15 @@
           <t>銀行</t>
         </is>
       </c>
-      <c r="C7" t="n">
-        <v>138.5</v>
-      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>17746424</v>
-      </c>
-      <c r="E7" t="n">
-        <v>2.37</v>
-      </c>
+        <v>14737451</v>
+      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-12</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -465,15 +465,23 @@
           <t>銀行</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="n">
+        <v>8.98</v>
+      </c>
       <c r="D2" t="n">
-        <v>248112067</v>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+        <v>247996067</v>
+      </c>
+      <c r="E2" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>🔥爆升</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
@@ -488,15 +496,19 @@
           <t>科技</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="n">
+        <v>26.2</v>
+      </c>
       <c r="D3" t="n">
-        <v>131885183</v>
-      </c>
-      <c r="E3" t="inlineStr"/>
+        <v>131880583</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1.39</v>
+      </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
@@ -511,15 +523,19 @@
           <t>科技</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="n">
+        <v>77.90000000000001</v>
+      </c>
       <c r="D4" t="n">
-        <v>47409244</v>
-      </c>
-      <c r="E4" t="inlineStr"/>
+        <v>47407244</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-0.26</v>
+      </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
@@ -534,15 +550,19 @@
           <t>科技</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="n">
+        <v>463.6</v>
+      </c>
       <c r="D5" t="n">
-        <v>22348046</v>
-      </c>
-      <c r="E5" t="inlineStr"/>
+        <v>22334646</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1.4</v>
+      </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
@@ -557,15 +577,19 @@
           <t>新能源</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="n">
+        <v>86.55</v>
+      </c>
       <c r="D6" t="n">
-        <v>16499792</v>
-      </c>
-      <c r="E6" t="inlineStr"/>
+        <v>16484892</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1.88</v>
+      </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>
@@ -580,15 +604,23 @@
           <t>銀行</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="n">
+        <v>142.8</v>
+      </c>
       <c r="D7" t="n">
-        <v>14737451</v>
-      </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
+        <v>14715851</v>
+      </c>
+      <c r="E7" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>🔥爆升</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-13</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -481,7 +481,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
     </row>
@@ -535,7 +535,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
     </row>
@@ -562,7 +562,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
     </row>
@@ -589,7 +589,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
     </row>
@@ -620,7 +620,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-14</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -466,22 +466,18 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8.98</v>
+        <v>8.91</v>
       </c>
       <c r="D2" t="n">
-        <v>247996067</v>
+        <v>213683528</v>
       </c>
       <c r="E2" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>🔥爆升</t>
-        </is>
-      </c>
+        <v>-0.78</v>
+      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -497,18 +493,18 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>26.2</v>
+        <v>26.26</v>
       </c>
       <c r="D3" t="n">
-        <v>131880583</v>
+        <v>94791143</v>
       </c>
       <c r="E3" t="n">
-        <v>1.39</v>
+        <v>0.23</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -524,18 +520,18 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>77.90000000000001</v>
+        <v>78.25</v>
       </c>
       <c r="D4" t="n">
-        <v>47407244</v>
+        <v>24420487</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.26</v>
+        <v>0.45</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -551,18 +547,18 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>463.6</v>
+        <v>459.6</v>
       </c>
       <c r="D5" t="n">
-        <v>22334646</v>
+        <v>19749038</v>
       </c>
       <c r="E5" t="n">
-        <v>1.4</v>
+        <v>-0.86</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -578,18 +574,18 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>86.55</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="D6" t="n">
-        <v>16484892</v>
+        <v>19539835</v>
       </c>
       <c r="E6" t="n">
-        <v>1.88</v>
+        <v>-1.1</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>
@@ -605,22 +601,18 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>142.8</v>
+        <v>145.8</v>
       </c>
       <c r="D7" t="n">
-        <v>14715851</v>
+        <v>19098018</v>
       </c>
       <c r="E7" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>🔥爆升</t>
-        </is>
-      </c>
+        <v>2.1</v>
+      </c>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-15</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -466,18 +466,18 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8.91</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>213683528</v>
+        <v>207688432</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.78</v>
+        <v>-0.22</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
@@ -493,18 +493,18 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>26.26</v>
+        <v>25.66</v>
       </c>
       <c r="D3" t="n">
-        <v>94791143</v>
+        <v>113820844</v>
       </c>
       <c r="E3" t="n">
-        <v>0.23</v>
+        <v>-2.28</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
@@ -520,18 +520,18 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>78.25</v>
+        <v>75.3</v>
       </c>
       <c r="D4" t="n">
-        <v>24420487</v>
+        <v>40106007</v>
       </c>
       <c r="E4" t="n">
-        <v>0.45</v>
+        <v>-3.77</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
@@ -547,18 +547,18 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>459.6</v>
+        <v>447.4</v>
       </c>
       <c r="D5" t="n">
-        <v>19749038</v>
+        <v>24325342</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.86</v>
+        <v>-2.65</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
@@ -574,18 +574,18 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>85.59999999999999</v>
+        <v>84.05</v>
       </c>
       <c r="D6" t="n">
-        <v>19539835</v>
+        <v>17291496</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.1</v>
+        <v>-1.81</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>
@@ -601,18 +601,18 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>145.8</v>
+        <v>146</v>
       </c>
       <c r="D7" t="n">
-        <v>19098018</v>
+        <v>10893838</v>
       </c>
       <c r="E7" t="n">
-        <v>2.1</v>
+        <v>0.14</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -466,18 +466,18 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8.890000000000001</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>207688432</v>
+        <v>199417941</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.22</v>
+        <v>-2.02</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
     </row>
@@ -493,52 +493,52 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>25.66</v>
+        <v>25.42</v>
       </c>
       <c r="D3" t="n">
-        <v>113820844</v>
+        <v>109311295</v>
       </c>
       <c r="E3" t="n">
-        <v>-2.28</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3690.HK</t>
+          <t>1211.HK</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>科技</t>
+          <t>新能源</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>75.3</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>40106007</v>
+        <v>26625914</v>
       </c>
       <c r="E4" t="n">
-        <v>-3.77</v>
+        <v>-2.56</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0700.HK</t>
+          <t>3690.HK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -547,72 +547,72 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>447.4</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="D5" t="n">
-        <v>24325342</v>
+        <v>22509016</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.65</v>
+        <v>-1.2</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1211.HK</t>
+          <t>0005.HK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>新能源</t>
+          <t>銀行</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>84.05</v>
+        <v>148</v>
       </c>
       <c r="D6" t="n">
-        <v>17291496</v>
+        <v>20033826</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.81</v>
+        <v>1.37</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0005.HK</t>
+          <t>0700.HK</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>銀行</t>
+          <t>科技</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>146</v>
+        <v>445.4</v>
       </c>
       <c r="D7" t="n">
-        <v>10893838</v>
+        <v>16962934</v>
       </c>
       <c r="E7" t="n">
-        <v>0.14</v>
+        <v>-0.45</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -466,18 +466,18 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8.710000000000001</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>199417941</v>
+        <v>336421078</v>
       </c>
       <c r="E2" t="n">
-        <v>-2.02</v>
+        <v>-1.03</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
     </row>
@@ -493,126 +493,126 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>25.42</v>
+        <v>24.58</v>
       </c>
       <c r="D3" t="n">
-        <v>109311295</v>
+        <v>199676198</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-3.3</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1211.HK</t>
+          <t>3690.HK</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>新能源</t>
+          <t>科技</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>81.90000000000001</v>
+        <v>71.8</v>
       </c>
       <c r="D4" t="n">
-        <v>26625914</v>
+        <v>68422090</v>
       </c>
       <c r="E4" t="n">
-        <v>-2.56</v>
+        <v>-3.49</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3690.HK</t>
+          <t>1211.HK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>科技</t>
+          <t>新能源</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>74.40000000000001</v>
+        <v>80.84999999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>22509016</v>
+        <v>30921772</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.2</v>
+        <v>-1.28</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0005.HK</t>
+          <t>0700.HK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>銀行</t>
+          <t>科技</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>148</v>
+        <v>440.2</v>
       </c>
       <c r="D6" t="n">
-        <v>20033826</v>
+        <v>30133517</v>
       </c>
       <c r="E6" t="n">
-        <v>1.37</v>
+        <v>-1.17</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0700.HK</t>
+          <t>0005.HK</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>科技</t>
+          <t>銀行</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>445.4</v>
+        <v>149</v>
       </c>
       <c r="D7" t="n">
-        <v>16962934</v>
+        <v>28019812</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.45</v>
+        <v>0.68</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -469,7 +469,7 @@
         <v>8.619999999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>336421078</v>
+        <v>335563078</v>
       </c>
       <c r="E2" t="n">
         <v>-1.03</v>
@@ -477,7 +477,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
@@ -496,7 +496,7 @@
         <v>24.58</v>
       </c>
       <c r="D3" t="n">
-        <v>199676198</v>
+        <v>199675798</v>
       </c>
       <c r="E3" t="n">
         <v>-3.3</v>
@@ -504,7 +504,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
@@ -523,7 +523,7 @@
         <v>71.8</v>
       </c>
       <c r="D4" t="n">
-        <v>68422090</v>
+        <v>68421090</v>
       </c>
       <c r="E4" t="n">
         <v>-3.49</v>
@@ -531,7 +531,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
@@ -550,7 +550,7 @@
         <v>80.84999999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>30921772</v>
+        <v>30913072</v>
       </c>
       <c r="E5" t="n">
         <v>-1.28</v>
@@ -558,7 +558,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
         <v>440.2</v>
       </c>
       <c r="D6" t="n">
-        <v>30133517</v>
+        <v>30119117</v>
       </c>
       <c r="E6" t="n">
         <v>-1.17</v>
@@ -585,7 +585,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>
@@ -612,7 +612,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -477,7 +477,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
     </row>
@@ -504,7 +504,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
     </row>
@@ -531,7 +531,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
     </row>
@@ -558,7 +558,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
     </row>
@@ -585,7 +585,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
     </row>
@@ -612,7 +612,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-20</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -477,7 +477,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
     </row>
@@ -504,7 +504,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
     </row>
@@ -531,7 +531,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
     </row>
@@ -558,7 +558,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
     </row>
@@ -585,7 +585,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
     </row>
@@ -612,7 +612,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-21</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -466,18 +466,18 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8.619999999999999</v>
+        <v>8.59</v>
       </c>
       <c r="D2" t="n">
-        <v>335563078</v>
+        <v>281837072</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.03</v>
+        <v>-0.35</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
     </row>
@@ -493,18 +493,18 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>24.58</v>
+        <v>23.72</v>
       </c>
       <c r="D3" t="n">
-        <v>199675798</v>
+        <v>241867064</v>
       </c>
       <c r="E3" t="n">
-        <v>-3.3</v>
+        <v>-3.5</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
     </row>
@@ -520,18 +520,18 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>71.8</v>
+        <v>72</v>
       </c>
       <c r="D4" t="n">
-        <v>68421090</v>
+        <v>57155017</v>
       </c>
       <c r="E4" t="n">
-        <v>-3.49</v>
+        <v>0.28</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
     </row>
@@ -547,18 +547,18 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>80.84999999999999</v>
+        <v>78.34999999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>30913072</v>
+        <v>40013285</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.28</v>
+        <v>-3.09</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
     </row>
@@ -574,18 +574,18 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>440.2</v>
+        <v>433</v>
       </c>
       <c r="D6" t="n">
-        <v>30119117</v>
+        <v>31563511</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.17</v>
+        <v>-1.64</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
     </row>
@@ -601,18 +601,18 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>149</v>
+        <v>147.9</v>
       </c>
       <c r="D7" t="n">
-        <v>28019812</v>
+        <v>11433704</v>
       </c>
       <c r="E7" t="n">
-        <v>0.68</v>
+        <v>-0.74</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-22</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -457,61 +457,61 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0939.HK</t>
+          <t>1810.HK</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>銀行</t>
+          <t>科技</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8.59</v>
+        <v>22.62</v>
       </c>
       <c r="D2" t="n">
-        <v>281837072</v>
+        <v>244562008</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.35</v>
+        <v>-4.64</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1810.HK</t>
+          <t>0939.HK</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>科技</t>
+          <t>銀行</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>23.72</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="D3" t="n">
-        <v>241867064</v>
+        <v>240187381</v>
       </c>
       <c r="E3" t="n">
-        <v>-3.5</v>
+        <v>0.47</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3690.HK</t>
+          <t>0700.HK</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -520,18 +520,18 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>72</v>
+        <v>414.8</v>
       </c>
       <c r="D4" t="n">
-        <v>57155017</v>
+        <v>43435989</v>
       </c>
       <c r="E4" t="n">
-        <v>0.28</v>
+        <v>-4.2</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
     </row>
@@ -547,25 +547,25 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>78.34999999999999</v>
+        <v>75.84999999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>40013285</v>
+        <v>38196900</v>
       </c>
       <c r="E5" t="n">
-        <v>-3.09</v>
+        <v>-3.19</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0700.HK</t>
+          <t>3690.HK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -574,18 +574,18 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>433</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="D6" t="n">
-        <v>31563511</v>
+        <v>33271403</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.64</v>
+        <v>-3.33</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
     </row>
@@ -601,18 +601,18 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>147.9</v>
+        <v>148.7</v>
       </c>
       <c r="D7" t="n">
-        <v>11433704</v>
+        <v>14753307</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.74</v>
+        <v>0.54</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -457,61 +457,61 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1810.HK</t>
+          <t>0939.HK</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>科技</t>
+          <t>銀行</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>22.62</v>
+        <v>8.49</v>
       </c>
       <c r="D2" t="n">
-        <v>244562008</v>
+        <v>253211961</v>
       </c>
       <c r="E2" t="n">
-        <v>-4.64</v>
+        <v>-1.62</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0939.HK</t>
+          <t>1810.HK</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>銀行</t>
+          <t>科技</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>8.630000000000001</v>
+        <v>22.96</v>
       </c>
       <c r="D3" t="n">
-        <v>240187381</v>
+        <v>219958418</v>
       </c>
       <c r="E3" t="n">
-        <v>0.47</v>
+        <v>1.5</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0700.HK</t>
+          <t>3690.HK</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -520,72 +520,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>414.8</v>
+        <v>67.75</v>
       </c>
       <c r="D4" t="n">
-        <v>43435989</v>
+        <v>53084562</v>
       </c>
       <c r="E4" t="n">
-        <v>-4.2</v>
+        <v>-2.66</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1211.HK</t>
+          <t>0700.HK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>新能源</t>
+          <t>科技</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>75.84999999999999</v>
+        <v>428.8</v>
       </c>
       <c r="D5" t="n">
-        <v>38196900</v>
+        <v>39960188</v>
       </c>
       <c r="E5" t="n">
-        <v>-3.19</v>
-      </c>
-      <c r="F5" t="inlineStr"/>
+        <v>3.38</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>🔥爆升</t>
+        </is>
+      </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>3690.HK</t>
+          <t>1211.HK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>科技</t>
+          <t>新能源</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>69.59999999999999</v>
+        <v>75.95</v>
       </c>
       <c r="D6" t="n">
-        <v>33271403</v>
+        <v>27134039</v>
       </c>
       <c r="E6" t="n">
-        <v>-3.33</v>
+        <v>0.13</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>
@@ -601,18 +605,18 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>148.7</v>
+        <v>148.2</v>
       </c>
       <c r="D7" t="n">
-        <v>14753307</v>
+        <v>10676559</v>
       </c>
       <c r="E7" t="n">
-        <v>0.54</v>
+        <v>-0.34</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -466,18 +466,18 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8.49</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>253211961</v>
+        <v>296655004</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.62</v>
+        <v>-2.24</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>
@@ -493,18 +493,18 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>22.96</v>
+        <v>22.3</v>
       </c>
       <c r="D3" t="n">
-        <v>219958418</v>
+        <v>178979826</v>
       </c>
       <c r="E3" t="n">
-        <v>1.5</v>
+        <v>-2.87</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>
@@ -520,18 +520,18 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>67.75</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="D4" t="n">
-        <v>53084562</v>
+        <v>63246885</v>
       </c>
       <c r="E4" t="n">
-        <v>-2.66</v>
+        <v>-2.44</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>
@@ -547,22 +547,18 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>428.8</v>
+        <v>421.4</v>
       </c>
       <c r="D5" t="n">
-        <v>39960188</v>
+        <v>29475228</v>
       </c>
       <c r="E5" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>🔥爆升</t>
-        </is>
-      </c>
+        <v>-1.73</v>
+      </c>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>
@@ -578,10 +574,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>75.95</v>
+        <v>76.05</v>
       </c>
       <c r="D6" t="n">
-        <v>27134039</v>
+        <v>28179889</v>
       </c>
       <c r="E6" t="n">
         <v>0.13</v>
@@ -589,7 +585,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>
@@ -605,18 +601,18 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>148.2</v>
+        <v>148.3</v>
       </c>
       <c r="D7" t="n">
-        <v>10676559</v>
+        <v>8640496</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.34</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -466,18 +466,18 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8.300000000000001</v>
+        <v>8.26</v>
       </c>
       <c r="D2" t="n">
-        <v>296655004</v>
+        <v>302272122</v>
       </c>
       <c r="E2" t="n">
-        <v>-2.24</v>
+        <v>-0.48</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
     </row>
@@ -493,18 +493,18 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>22.3</v>
+        <v>21.42</v>
       </c>
       <c r="D3" t="n">
-        <v>178979826</v>
+        <v>191629568</v>
       </c>
       <c r="E3" t="n">
-        <v>-2.87</v>
+        <v>-3.95</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
     </row>
@@ -520,72 +520,72 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>66.09999999999999</v>
+        <v>64.25</v>
       </c>
       <c r="D4" t="n">
-        <v>63246885</v>
+        <v>84458170</v>
       </c>
       <c r="E4" t="n">
-        <v>-2.44</v>
+        <v>-2.8</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0700.HK</t>
+          <t>1211.HK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>科技</t>
+          <t>新能源</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>421.4</v>
+        <v>72.65000000000001</v>
       </c>
       <c r="D5" t="n">
-        <v>29475228</v>
+        <v>32626256</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.73</v>
+        <v>-4.47</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1211.HK</t>
+          <t>0700.HK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>新能源</t>
+          <t>科技</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>76.05</v>
+        <v>411.8</v>
       </c>
       <c r="D6" t="n">
-        <v>28179889</v>
+        <v>31873009</v>
       </c>
       <c r="E6" t="n">
-        <v>0.13</v>
+        <v>-2.28</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
     </row>
@@ -601,18 +601,18 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>148.3</v>
+        <v>147.7</v>
       </c>
       <c r="D7" t="n">
-        <v>8640496</v>
+        <v>17958541</v>
       </c>
       <c r="E7" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.4</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -469,7 +469,7 @@
         <v>8.26</v>
       </c>
       <c r="D2" t="n">
-        <v>302272122</v>
+        <v>301316122</v>
       </c>
       <c r="E2" t="n">
         <v>-0.48</v>
@@ -477,7 +477,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
     </row>
@@ -496,7 +496,7 @@
         <v>21.42</v>
       </c>
       <c r="D3" t="n">
-        <v>191629568</v>
+        <v>191622768</v>
       </c>
       <c r="E3" t="n">
         <v>-3.95</v>
@@ -504,7 +504,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
     </row>
@@ -523,7 +523,7 @@
         <v>64.25</v>
       </c>
       <c r="D4" t="n">
-        <v>84458170</v>
+        <v>84453570</v>
       </c>
       <c r="E4" t="n">
         <v>-2.8</v>
@@ -531,7 +531,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
     </row>
@@ -550,7 +550,7 @@
         <v>72.65000000000001</v>
       </c>
       <c r="D5" t="n">
-        <v>32626256</v>
+        <v>32623656</v>
       </c>
       <c r="E5" t="n">
         <v>-4.47</v>
@@ -558,7 +558,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
         <v>411.8</v>
       </c>
       <c r="D6" t="n">
-        <v>31873009</v>
+        <v>31872909</v>
       </c>
       <c r="E6" t="n">
         <v>-2.28</v>
@@ -585,7 +585,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
     </row>
@@ -604,7 +604,7 @@
         <v>147.7</v>
       </c>
       <c r="D7" t="n">
-        <v>17958541</v>
+        <v>17958141</v>
       </c>
       <c r="E7" t="n">
         <v>-0.4</v>
@@ -612,7 +612,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -477,7 +477,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
     </row>
@@ -504,7 +504,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
     </row>
@@ -531,7 +531,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
     </row>
@@ -558,7 +558,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
     </row>
@@ -585,7 +585,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
     </row>
@@ -612,7 +612,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-28</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -457,54 +457,54 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0939.HK</t>
+          <t>1810.HK</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>銀行</t>
+          <t>科技</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8.26</v>
+        <v>21.86</v>
       </c>
       <c r="D2" t="n">
-        <v>301316122</v>
+        <v>206098162</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.48</v>
+        <v>2.05</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1810.HK</t>
+          <t>0939.HK</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>科技</t>
+          <t>銀行</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>21.42</v>
+        <v>8.24</v>
       </c>
       <c r="D3" t="n">
-        <v>191622768</v>
+        <v>203630574</v>
       </c>
       <c r="E3" t="n">
-        <v>-3.95</v>
+        <v>-0.24</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
@@ -520,72 +520,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>64.25</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>84453570</v>
+        <v>79469292</v>
       </c>
       <c r="E4" t="n">
-        <v>-2.8</v>
-      </c>
-      <c r="F4" t="inlineStr"/>
+        <v>5.29</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>🔥爆升</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1211.HK</t>
+          <t>0700.HK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>新能源</t>
+          <t>科技</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>72.65000000000001</v>
+        <v>420.2</v>
       </c>
       <c r="D5" t="n">
-        <v>32623656</v>
+        <v>33068270</v>
       </c>
       <c r="E5" t="n">
-        <v>-4.47</v>
+        <v>2.04</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0700.HK</t>
+          <t>1211.HK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>科技</t>
+          <t>新能源</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>411.8</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="D6" t="n">
-        <v>31872909</v>
+        <v>24806382</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.28</v>
+        <v>0.34</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>
@@ -601,18 +605,18 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>147.7</v>
+        <v>147.6</v>
       </c>
       <c r="D7" t="n">
-        <v>17958141</v>
+        <v>14017945</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.4</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-29</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -457,54 +457,54 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1810.HK</t>
+          <t>0939.HK</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>科技</t>
+          <t>銀行</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>21.86</v>
+        <v>8.07</v>
       </c>
       <c r="D2" t="n">
-        <v>206098162</v>
+        <v>446083435</v>
       </c>
       <c r="E2" t="n">
-        <v>2.05</v>
+        <v>-2.06</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0939.HK</t>
+          <t>1810.HK</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>銀行</t>
+          <t>科技</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>8.24</v>
+        <v>21.64</v>
       </c>
       <c r="D3" t="n">
-        <v>203630574</v>
+        <v>173878474</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.24</v>
+        <v>-1.01</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
     </row>
@@ -520,22 +520,18 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>67.65000000000001</v>
+        <v>68.5</v>
       </c>
       <c r="D4" t="n">
-        <v>79469292</v>
+        <v>65133829</v>
       </c>
       <c r="E4" t="n">
-        <v>5.29</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>🔥爆升</t>
-        </is>
-      </c>
+        <v>1.26</v>
+      </c>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
     </row>
@@ -551,18 +547,18 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>420.2</v>
+        <v>429.8</v>
       </c>
       <c r="D5" t="n">
-        <v>33068270</v>
+        <v>38994509</v>
       </c>
       <c r="E5" t="n">
-        <v>2.04</v>
+        <v>2.28</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
     </row>
@@ -578,18 +574,18 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>72.90000000000001</v>
+        <v>72.45</v>
       </c>
       <c r="D6" t="n">
-        <v>24806382</v>
+        <v>28317939</v>
       </c>
       <c r="E6" t="n">
-        <v>0.34</v>
+        <v>-0.62</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
     </row>
@@ -605,18 +601,18 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>147.6</v>
+        <v>147.9</v>
       </c>
       <c r="D7" t="n">
-        <v>14017945</v>
+        <v>13125169</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -469,7 +469,7 @@
         <v>8.07</v>
       </c>
       <c r="D2" t="n">
-        <v>446083435</v>
+        <v>446077435</v>
       </c>
       <c r="E2" t="n">
         <v>-2.06</v>
@@ -477,7 +477,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
@@ -496,7 +496,7 @@
         <v>21.64</v>
       </c>
       <c r="D3" t="n">
-        <v>173878474</v>
+        <v>173878074</v>
       </c>
       <c r="E3" t="n">
         <v>-1.01</v>
@@ -504,7 +504,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
@@ -531,7 +531,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
@@ -550,7 +550,7 @@
         <v>429.8</v>
       </c>
       <c r="D5" t="n">
-        <v>38994509</v>
+        <v>38994409</v>
       </c>
       <c r="E5" t="n">
         <v>2.28</v>
@@ -558,7 +558,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
         <v>72.45</v>
       </c>
       <c r="D6" t="n">
-        <v>28317939</v>
+        <v>28317739</v>
       </c>
       <c r="E6" t="n">
         <v>-0.62</v>
@@ -585,7 +585,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>
@@ -604,7 +604,7 @@
         <v>147.9</v>
       </c>
       <c r="D7" t="n">
-        <v>13125169</v>
+        <v>13123569</v>
       </c>
       <c r="E7" t="n">
         <v>0.2</v>
@@ -612,7 +612,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -466,18 +466,18 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8.07</v>
+        <v>7.84</v>
       </c>
       <c r="D2" t="n">
-        <v>446077435</v>
+        <v>347782413</v>
       </c>
       <c r="E2" t="n">
-        <v>-2.06</v>
+        <v>-0.34</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
     </row>
@@ -493,18 +493,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>21.64</v>
+        <v>22.6</v>
       </c>
       <c r="D3" t="n">
-        <v>173878074</v>
+        <v>222813369</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.01</v>
-      </c>
-      <c r="F3" t="inlineStr"/>
+        <v>4.44</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>🔥爆升</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
     </row>
@@ -520,72 +524,80 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>68.5</v>
+        <v>70.84999999999999</v>
       </c>
       <c r="D4" t="n">
-        <v>65133829</v>
+        <v>68123030</v>
       </c>
       <c r="E4" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="F4" t="inlineStr"/>
+        <v>3.43</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>🔥爆升</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0700.HK</t>
+          <t>1211.HK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>科技</t>
+          <t>新能源</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>429.8</v>
+        <v>78.3</v>
       </c>
       <c r="D5" t="n">
-        <v>38994409</v>
+        <v>54576171</v>
       </c>
       <c r="E5" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="F5" t="inlineStr"/>
+        <v>8.07</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>🔥爆升</t>
+        </is>
+      </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1211.HK</t>
+          <t>0700.HK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>新能源</t>
+          <t>科技</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>72.45</v>
+        <v>430.2</v>
       </c>
       <c r="D6" t="n">
-        <v>28317739</v>
+        <v>40905200</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.62</v>
+        <v>0.09</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
     </row>
@@ -601,18 +613,18 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>147.9</v>
+        <v>149.5</v>
       </c>
       <c r="D7" t="n">
-        <v>13123569</v>
+        <v>18648715</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2</v>
+        <v>1.08</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -457,80 +457,76 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0939.HK</t>
+          <t>1810.HK</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>銀行</t>
+          <t>科技</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7.84</v>
+        <v>22.96</v>
       </c>
       <c r="D2" t="n">
-        <v>347782413</v>
+        <v>268236962</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.34</v>
+        <v>1.59</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1810.HK</t>
+          <t>0939.HK</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>科技</t>
+          <t>銀行</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>22.6</v>
+        <v>7.78</v>
       </c>
       <c r="D3" t="n">
-        <v>222813369</v>
+        <v>226825441</v>
       </c>
       <c r="E3" t="n">
-        <v>4.44</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>🔥爆升</t>
-        </is>
-      </c>
+        <v>-0.77</v>
+      </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3690.HK</t>
+          <t>1211.HK</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>科技</t>
+          <t>新能源</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>70.84999999999999</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="D4" t="n">
-        <v>68123030</v>
+        <v>54233110</v>
       </c>
       <c r="E4" t="n">
-        <v>3.43</v>
+        <v>7.41</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -539,92 +535,88 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1211.HK</t>
+          <t>3690.HK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>新能源</t>
+          <t>科技</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>78.3</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>54576171</v>
+        <v>33746748</v>
       </c>
       <c r="E5" t="n">
-        <v>8.07</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>🔥爆升</t>
-        </is>
-      </c>
+        <v>1.06</v>
+      </c>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0700.HK</t>
+          <t>0005.HK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>科技</t>
+          <t>銀行</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>430.2</v>
+        <v>152</v>
       </c>
       <c r="D6" t="n">
-        <v>40905200</v>
+        <v>29830805</v>
       </c>
       <c r="E6" t="n">
-        <v>0.09</v>
+        <v>1.67</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0005.HK</t>
+          <t>0700.HK</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>銀行</t>
+          <t>科技</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>149.5</v>
+        <v>431.2</v>
       </c>
       <c r="D7" t="n">
-        <v>18648715</v>
+        <v>24957596</v>
       </c>
       <c r="E7" t="n">
-        <v>1.08</v>
+        <v>0.23</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -469,7 +469,7 @@
         <v>22.96</v>
       </c>
       <c r="D2" t="n">
-        <v>268236962</v>
+        <v>268232162</v>
       </c>
       <c r="E2" t="n">
         <v>1.59</v>
@@ -477,7 +477,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
@@ -496,7 +496,7 @@
         <v>7.78</v>
       </c>
       <c r="D3" t="n">
-        <v>226825441</v>
+        <v>226824441</v>
       </c>
       <c r="E3" t="n">
         <v>-0.77</v>
@@ -504,7 +504,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
@@ -523,7 +523,7 @@
         <v>84.09999999999999</v>
       </c>
       <c r="D4" t="n">
-        <v>54233110</v>
+        <v>54232910</v>
       </c>
       <c r="E4" t="n">
         <v>7.41</v>
@@ -535,7 +535,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
@@ -554,7 +554,7 @@
         <v>71.59999999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>33746748</v>
+        <v>33741448</v>
       </c>
       <c r="E5" t="n">
         <v>1.06</v>
@@ -562,7 +562,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
@@ -581,7 +581,7 @@
         <v>152</v>
       </c>
       <c r="D6" t="n">
-        <v>29830805</v>
+        <v>29828005</v>
       </c>
       <c r="E6" t="n">
         <v>1.67</v>
@@ -589,7 +589,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>
@@ -608,7 +608,7 @@
         <v>431.2</v>
       </c>
       <c r="D7" t="n">
-        <v>24957596</v>
+        <v>24957296</v>
       </c>
       <c r="E7" t="n">
         <v>0.23</v>
@@ -616,7 +616,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-04</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -477,7 +477,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
     </row>
@@ -504,7 +504,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
     </row>
@@ -535,7 +535,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
     </row>
@@ -562,7 +562,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
     </row>
@@ -589,7 +589,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
     </row>
@@ -616,7 +616,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-05</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -457,76 +457,76 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1810.HK</t>
+          <t>0939.HK</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>科技</t>
+          <t>銀行</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>22.96</v>
+        <v>7.85</v>
       </c>
       <c r="D2" t="n">
-        <v>268232162</v>
+        <v>204470175</v>
       </c>
       <c r="E2" t="n">
-        <v>1.59</v>
+        <v>0.9</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0939.HK</t>
+          <t>1810.HK</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>銀行</t>
+          <t>科技</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7.78</v>
+        <v>23.28</v>
       </c>
       <c r="D3" t="n">
-        <v>226824441</v>
+        <v>160206188</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.77</v>
+        <v>1.39</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1211.HK</t>
+          <t>3690.HK</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>新能源</t>
+          <t>科技</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>84.09999999999999</v>
+        <v>74.95</v>
       </c>
       <c r="D4" t="n">
-        <v>54232910</v>
+        <v>50532484</v>
       </c>
       <c r="E4" t="n">
-        <v>7.41</v>
+        <v>4.68</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -535,14 +535,14 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3690.HK</t>
+          <t>0700.HK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,72 +551,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>71.59999999999999</v>
+        <v>452</v>
       </c>
       <c r="D5" t="n">
-        <v>33741448</v>
+        <v>41502283</v>
       </c>
       <c r="E5" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="F5" t="inlineStr"/>
+        <v>4.82</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>🔥爆升</t>
+        </is>
+      </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0005.HK</t>
+          <t>1211.HK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>銀行</t>
+          <t>新能源</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>152</v>
+        <v>83.8</v>
       </c>
       <c r="D6" t="n">
-        <v>29828005</v>
+        <v>36021501</v>
       </c>
       <c r="E6" t="n">
-        <v>1.67</v>
+        <v>-0.36</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0700.HK</t>
+          <t>0005.HK</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>科技</t>
+          <t>銀行</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>431.2</v>
+        <v>152</v>
       </c>
       <c r="D7" t="n">
-        <v>24957296</v>
+        <v>11330076</v>
       </c>
       <c r="E7" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-06</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -457,54 +457,54 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0939.HK</t>
+          <t>1810.HK</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>銀行</t>
+          <t>科技</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7.85</v>
+        <v>23.1</v>
       </c>
       <c r="D2" t="n">
-        <v>204470175</v>
+        <v>202757949</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9</v>
+        <v>-0.77</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1810.HK</t>
+          <t>0939.HK</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>科技</t>
+          <t>銀行</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>23.28</v>
+        <v>7.83</v>
       </c>
       <c r="D3" t="n">
-        <v>160206188</v>
+        <v>194336167</v>
       </c>
       <c r="E3" t="n">
-        <v>1.39</v>
+        <v>-0.25</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
     </row>
@@ -520,13 +520,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>74.95</v>
+        <v>78.34999999999999</v>
       </c>
       <c r="D4" t="n">
-        <v>50532484</v>
+        <v>117136479</v>
       </c>
       <c r="E4" t="n">
-        <v>4.68</v>
+        <v>4.54</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -535,7 +535,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
     </row>
@@ -551,22 +551,18 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>452</v>
+        <v>461.2</v>
       </c>
       <c r="D5" t="n">
-        <v>41502283</v>
+        <v>55418634</v>
       </c>
       <c r="E5" t="n">
-        <v>4.82</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>🔥爆升</t>
-        </is>
-      </c>
+        <v>2.04</v>
+      </c>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
     </row>
@@ -582,18 +578,18 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>83.8</v>
+        <v>83.45</v>
       </c>
       <c r="D6" t="n">
-        <v>36021501</v>
+        <v>26025082</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.36</v>
+        <v>-0.42</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
     </row>
@@ -609,18 +605,18 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>152</v>
+        <v>153.3</v>
       </c>
       <c r="D7" t="n">
-        <v>11330076</v>
+        <v>13821429</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>0.86</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -466,18 +466,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>23.1</v>
+        <v>25.3</v>
       </c>
       <c r="D2" t="n">
-        <v>202757949</v>
+        <v>409721793</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.77</v>
-      </c>
-      <c r="F2" t="inlineStr"/>
+        <v>9.52</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>🔥爆升</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
     </row>
@@ -493,18 +497,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7.83</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="D3" t="n">
-        <v>194336167</v>
+        <v>291435740</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="F3" t="inlineStr"/>
+        <v>5.75</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>🔥爆升</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
     </row>
@@ -520,13 +528,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>78.34999999999999</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>117136479</v>
+        <v>72751380</v>
       </c>
       <c r="E4" t="n">
-        <v>4.54</v>
+        <v>3.25</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -535,7 +543,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
     </row>
@@ -551,18 +559,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>461.2</v>
+        <v>478.8</v>
       </c>
       <c r="D5" t="n">
-        <v>55418634</v>
+        <v>56278727</v>
       </c>
       <c r="E5" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="F5" t="inlineStr"/>
+        <v>3.82</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>🔥爆升</t>
+        </is>
+      </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
     </row>
@@ -578,18 +590,18 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>83.45</v>
+        <v>85.84999999999999</v>
       </c>
       <c r="D6" t="n">
-        <v>26025082</v>
+        <v>26821234</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.42</v>
+        <v>2.88</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
     </row>
@@ -605,18 +617,18 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>153.3</v>
+        <v>151.9</v>
       </c>
       <c r="D7" t="n">
-        <v>13821429</v>
+        <v>10813938</v>
       </c>
       <c r="E7" t="n">
-        <v>0.86</v>
+        <v>-0.91</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -466,22 +466,18 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>25.3</v>
+        <v>25</v>
       </c>
       <c r="D2" t="n">
-        <v>409721793</v>
+        <v>348624328</v>
       </c>
       <c r="E2" t="n">
-        <v>9.52</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>🔥爆升</t>
-        </is>
-      </c>
+        <v>-1.19</v>
+      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
@@ -497,22 +493,18 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>8.279999999999999</v>
+        <v>8.07</v>
       </c>
       <c r="D3" t="n">
-        <v>291435740</v>
+        <v>212661134</v>
       </c>
       <c r="E3" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>🔥爆升</t>
-        </is>
-      </c>
+        <v>-2.54</v>
+      </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
@@ -528,22 +520,18 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>80.90000000000001</v>
+        <v>78.5</v>
       </c>
       <c r="D4" t="n">
-        <v>72751380</v>
+        <v>55806031</v>
       </c>
       <c r="E4" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>🔥爆升</t>
-        </is>
-      </c>
+        <v>-2.97</v>
+      </c>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
@@ -559,22 +547,18 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>478.8</v>
+        <v>469.6</v>
       </c>
       <c r="D5" t="n">
-        <v>56278727</v>
+        <v>42402252</v>
       </c>
       <c r="E5" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>🔥爆升</t>
-        </is>
-      </c>
+        <v>-1.92</v>
+      </c>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
@@ -590,18 +574,18 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>85.84999999999999</v>
+        <v>82.65000000000001</v>
       </c>
       <c r="D6" t="n">
-        <v>26821234</v>
+        <v>38997658</v>
       </c>
       <c r="E6" t="n">
-        <v>2.88</v>
+        <v>-3.73</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>
@@ -617,18 +601,18 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>151.9</v>
+        <v>152.3</v>
       </c>
       <c r="D7" t="n">
-        <v>10813938</v>
+        <v>8992816</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.91</v>
+        <v>0.26</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -466,18 +466,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>25</v>
+        <v>25.84</v>
       </c>
       <c r="D2" t="n">
-        <v>348624328</v>
+        <v>254499994</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.19</v>
-      </c>
-      <c r="F2" t="inlineStr"/>
+        <v>3.36</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>🔥爆升</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
     </row>
@@ -493,25 +497,25 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>8.07</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="D3" t="n">
-        <v>212661134</v>
+        <v>157134844</v>
       </c>
       <c r="E3" t="n">
-        <v>-2.54</v>
+        <v>0.74</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3690.HK</t>
+          <t>0700.HK</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -520,25 +524,25 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>78.5</v>
+        <v>460.2</v>
       </c>
       <c r="D4" t="n">
-        <v>55806031</v>
+        <v>40440798</v>
       </c>
       <c r="E4" t="n">
-        <v>-2.97</v>
+        <v>-2</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0700.HK</t>
+          <t>3690.HK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -547,18 +551,18 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>469.6</v>
+        <v>78.7</v>
       </c>
       <c r="D5" t="n">
-        <v>42402252</v>
+        <v>38060521</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.92</v>
+        <v>0.25</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
     </row>
@@ -574,18 +578,18 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>82.65000000000001</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="D6" t="n">
-        <v>38997658</v>
+        <v>23566417</v>
       </c>
       <c r="E6" t="n">
-        <v>-3.73</v>
+        <v>2.72</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
     </row>
@@ -601,18 +605,18 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>152.3</v>
+        <v>153.5</v>
       </c>
       <c r="D7" t="n">
-        <v>8992816</v>
+        <v>11228812</v>
       </c>
       <c r="E7" t="n">
-        <v>0.26</v>
+        <v>0.79</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -469,7 +469,7 @@
         <v>25.84</v>
       </c>
       <c r="D2" t="n">
-        <v>254499994</v>
+        <v>254498794</v>
       </c>
       <c r="E2" t="n">
         <v>3.36</v>
@@ -481,7 +481,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
@@ -500,7 +500,7 @@
         <v>8.130000000000001</v>
       </c>
       <c r="D3" t="n">
-        <v>157134844</v>
+        <v>157131844</v>
       </c>
       <c r="E3" t="n">
         <v>0.74</v>
@@ -508,7 +508,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
@@ -527,7 +527,7 @@
         <v>460.2</v>
       </c>
       <c r="D4" t="n">
-        <v>40440798</v>
+        <v>40440298</v>
       </c>
       <c r="E4" t="n">
         <v>-2</v>
@@ -535,7 +535,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
@@ -554,7 +554,7 @@
         <v>78.7</v>
       </c>
       <c r="D5" t="n">
-        <v>38060521</v>
+        <v>38059821</v>
       </c>
       <c r="E5" t="n">
         <v>0.25</v>
@@ -562,7 +562,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
@@ -581,7 +581,7 @@
         <v>84.90000000000001</v>
       </c>
       <c r="D6" t="n">
-        <v>23566417</v>
+        <v>23565217</v>
       </c>
       <c r="E6" t="n">
         <v>2.72</v>
@@ -589,7 +589,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>
@@ -608,7 +608,7 @@
         <v>153.5</v>
       </c>
       <c r="D7" t="n">
-        <v>11228812</v>
+        <v>11223212</v>
       </c>
       <c r="E7" t="n">
         <v>0.79</v>
@@ -616,7 +616,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-11</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -481,7 +481,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
     </row>
@@ -535,7 +535,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
     </row>
@@ -562,7 +562,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
     </row>
@@ -589,7 +589,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
     </row>
@@ -616,7 +616,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-12</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -469,19 +469,15 @@
         <v>25.84</v>
       </c>
       <c r="D2" t="n">
-        <v>254498794</v>
+        <v>206565061</v>
       </c>
       <c r="E2" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>🔥爆升</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -497,25 +493,25 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>8.130000000000001</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="D3" t="n">
-        <v>157131844</v>
+        <v>166773706</v>
       </c>
       <c r="E3" t="n">
-        <v>0.74</v>
+        <v>1.11</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0700.HK</t>
+          <t>3690.HK</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -524,25 +520,25 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>460.2</v>
+        <v>77.95</v>
       </c>
       <c r="D4" t="n">
-        <v>40440298</v>
+        <v>40168127</v>
       </c>
       <c r="E4" t="n">
-        <v>-2</v>
+        <v>-0.95</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3690.HK</t>
+          <t>0700.HK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -551,18 +547,18 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>78.7</v>
+        <v>457.6</v>
       </c>
       <c r="D5" t="n">
-        <v>38059821</v>
+        <v>24291942</v>
       </c>
       <c r="E5" t="n">
-        <v>0.25</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -578,18 +574,18 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>84.90000000000001</v>
+        <v>83.95</v>
       </c>
       <c r="D6" t="n">
-        <v>23565217</v>
+        <v>15518597</v>
       </c>
       <c r="E6" t="n">
-        <v>2.72</v>
+        <v>-1.12</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>
@@ -605,18 +601,18 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>153.5</v>
+        <v>153.8</v>
       </c>
       <c r="D7" t="n">
-        <v>11223212</v>
+        <v>7634322</v>
       </c>
       <c r="E7" t="n">
-        <v>0.79</v>
+        <v>0.2</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -466,18 +466,18 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>25.84</v>
+        <v>26.04</v>
       </c>
       <c r="D2" t="n">
-        <v>206565061</v>
+        <v>235765661</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>0.77</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
     </row>
@@ -493,18 +493,18 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>8.220000000000001</v>
+        <v>8.18</v>
       </c>
       <c r="D3" t="n">
-        <v>166773706</v>
+        <v>166094532</v>
       </c>
       <c r="E3" t="n">
-        <v>1.11</v>
+        <v>-0.49</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
     </row>
@@ -520,18 +520,18 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>77.95</v>
+        <v>79.2</v>
       </c>
       <c r="D4" t="n">
-        <v>40168127</v>
+        <v>50007153</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.95</v>
+        <v>1.6</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
     </row>
@@ -547,18 +547,18 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>457.6</v>
+        <v>456.2</v>
       </c>
       <c r="D5" t="n">
-        <v>24291942</v>
+        <v>25540840</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.31</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
     </row>
@@ -574,18 +574,18 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>83.95</v>
+        <v>86.15000000000001</v>
       </c>
       <c r="D6" t="n">
-        <v>15518597</v>
+        <v>23042274</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.12</v>
+        <v>2.62</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
     </row>
@@ -601,18 +601,18 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>153.8</v>
+        <v>152.6</v>
       </c>
       <c r="D7" t="n">
-        <v>7634322</v>
+        <v>10673356</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2</v>
+        <v>-0.78</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -457,54 +457,54 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1810.HK</t>
+          <t>0939.HK</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>科技</t>
+          <t>銀行</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>26.04</v>
+        <v>8.17</v>
       </c>
       <c r="D2" t="n">
-        <v>235765661</v>
+        <v>197107218</v>
       </c>
       <c r="E2" t="n">
-        <v>0.77</v>
+        <v>-0.12</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0939.HK</t>
+          <t>1810.HK</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>銀行</t>
+          <t>科技</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>8.18</v>
+        <v>25.86</v>
       </c>
       <c r="D3" t="n">
-        <v>166094532</v>
+        <v>151795385</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.49</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
     </row>
@@ -520,18 +520,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>79.2</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>50007153</v>
+        <v>88087018</v>
       </c>
       <c r="E4" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="F4" t="inlineStr"/>
+        <v>5.3</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>🔥爆升</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
     </row>
@@ -547,18 +551,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>456.2</v>
+        <v>474</v>
       </c>
       <c r="D5" t="n">
-        <v>25540840</v>
+        <v>33782856</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.31</v>
-      </c>
-      <c r="F5" t="inlineStr"/>
+        <v>3.9</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>🔥爆升</t>
+        </is>
+      </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
     </row>
@@ -574,18 +582,18 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>86.15000000000001</v>
+        <v>86.95</v>
       </c>
       <c r="D6" t="n">
-        <v>23042274</v>
+        <v>18754137</v>
       </c>
       <c r="E6" t="n">
-        <v>2.62</v>
+        <v>0.93</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
     </row>
@@ -601,18 +609,18 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>152.6</v>
+        <v>155.3</v>
       </c>
       <c r="D7" t="n">
-        <v>10673356</v>
+        <v>15261193</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.78</v>
+        <v>1.77</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -457,54 +457,58 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0939.HK</t>
+          <t>1810.HK</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>銀行</t>
+          <t>科技</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8.17</v>
+        <v>27.5</v>
       </c>
       <c r="D2" t="n">
-        <v>197107218</v>
+        <v>319311911</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="F2" t="inlineStr"/>
+        <v>6.34</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>🔥爆升</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1810.HK</t>
+          <t>0939.HK</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>科技</t>
+          <t>銀行</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>25.86</v>
+        <v>8.19</v>
       </c>
       <c r="D3" t="n">
-        <v>151795385</v>
+        <v>216414488</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.6899999999999999</v>
+        <v>0.24</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -520,13 +524,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>83.40000000000001</v>
+        <v>87.2</v>
       </c>
       <c r="D4" t="n">
-        <v>88087018</v>
+        <v>100388958</v>
       </c>
       <c r="E4" t="n">
-        <v>5.3</v>
+        <v>4.56</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -535,7 +539,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -551,22 +555,18 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>474</v>
+        <v>484</v>
       </c>
       <c r="D5" t="n">
-        <v>33782856</v>
+        <v>42851575</v>
       </c>
       <c r="E5" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>🔥爆升</t>
-        </is>
-      </c>
+        <v>2.11</v>
+      </c>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -582,18 +582,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>86.95</v>
+        <v>90.95</v>
       </c>
       <c r="D6" t="n">
-        <v>18754137</v>
+        <v>34557521</v>
       </c>
       <c r="E6" t="n">
-        <v>0.93</v>
-      </c>
-      <c r="F6" t="inlineStr"/>
+        <v>4.6</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>🔥爆升</t>
+        </is>
+      </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>
@@ -609,18 +613,18 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>155.3</v>
+        <v>156.9</v>
       </c>
       <c r="D7" t="n">
-        <v>15261193</v>
+        <v>13901518</v>
       </c>
       <c r="E7" t="n">
-        <v>1.77</v>
+        <v>1.03</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -466,22 +466,18 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>27.5</v>
+        <v>26.88</v>
       </c>
       <c r="D2" t="n">
-        <v>319311911</v>
+        <v>279985322</v>
       </c>
       <c r="E2" t="n">
-        <v>6.34</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>🔥爆升</t>
-        </is>
-      </c>
+        <v>-2.25</v>
+      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
     </row>
@@ -497,18 +493,18 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>8.19</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="D3" t="n">
-        <v>216414488</v>
+        <v>246024201</v>
       </c>
       <c r="E3" t="n">
-        <v>0.24</v>
+        <v>1.22</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
     </row>
@@ -524,22 +520,18 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>87.2</v>
+        <v>83.65000000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>100388958</v>
+        <v>79212929</v>
       </c>
       <c r="E4" t="n">
-        <v>4.56</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>🔥爆升</t>
-        </is>
-      </c>
+        <v>-4.07</v>
+      </c>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
     </row>
@@ -555,18 +547,18 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>484</v>
+        <v>461.6</v>
       </c>
       <c r="D5" t="n">
-        <v>42851575</v>
+        <v>36238357</v>
       </c>
       <c r="E5" t="n">
-        <v>2.11</v>
+        <v>-4.63</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
     </row>
@@ -582,22 +574,18 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>90.95</v>
+        <v>88.7</v>
       </c>
       <c r="D6" t="n">
-        <v>34557521</v>
+        <v>26435625</v>
       </c>
       <c r="E6" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>🔥爆升</t>
-        </is>
-      </c>
+        <v>-2.47</v>
+      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
     </row>
@@ -616,15 +604,15 @@
         <v>156.9</v>
       </c>
       <c r="D7" t="n">
-        <v>13901518</v>
+        <v>17656635</v>
       </c>
       <c r="E7" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -469,7 +469,7 @@
         <v>26.88</v>
       </c>
       <c r="D2" t="n">
-        <v>279985322</v>
+        <v>279882322</v>
       </c>
       <c r="E2" t="n">
         <v>-2.25</v>
@@ -477,7 +477,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
@@ -496,7 +496,7 @@
         <v>8.289999999999999</v>
       </c>
       <c r="D3" t="n">
-        <v>246024201</v>
+        <v>245973201</v>
       </c>
       <c r="E3" t="n">
         <v>1.22</v>
@@ -504,7 +504,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
@@ -523,7 +523,7 @@
         <v>83.65000000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>79212929</v>
+        <v>79212029</v>
       </c>
       <c r="E4" t="n">
         <v>-4.07</v>
@@ -531,7 +531,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
@@ -550,7 +550,7 @@
         <v>461.6</v>
       </c>
       <c r="D5" t="n">
-        <v>36238357</v>
+        <v>36237657</v>
       </c>
       <c r="E5" t="n">
         <v>-4.63</v>
@@ -558,7 +558,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
         <v>88.7</v>
       </c>
       <c r="D6" t="n">
-        <v>26435625</v>
+        <v>26427225</v>
       </c>
       <c r="E6" t="n">
         <v>-2.47</v>
@@ -585,7 +585,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>
@@ -604,7 +604,7 @@
         <v>156.9</v>
       </c>
       <c r="D7" t="n">
-        <v>17656635</v>
+        <v>17653835</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -612,7 +612,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-18</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -477,7 +477,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -504,7 +504,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -531,7 +531,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -558,7 +558,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -585,7 +585,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>
@@ -612,7 +612,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-19</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -457,54 +457,62 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1810.HK</t>
+          <t>0939.HK</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>科技</t>
+          <t>銀行</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>26.88</v>
+        <v>8.65</v>
       </c>
       <c r="D2" t="n">
-        <v>279882322</v>
+        <v>370182314</v>
       </c>
       <c r="E2" t="n">
-        <v>-2.25</v>
-      </c>
-      <c r="F2" t="inlineStr"/>
+        <v>4.34</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>🔥爆升</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0939.HK</t>
+          <t>1810.HK</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>銀行</t>
+          <t>科技</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>8.289999999999999</v>
+        <v>27.74</v>
       </c>
       <c r="D3" t="n">
-        <v>245973201</v>
+        <v>167547503</v>
       </c>
       <c r="E3" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="F3" t="inlineStr"/>
+        <v>3.2</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>🔥爆升</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
@@ -520,18 +528,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>83.65000000000001</v>
+        <v>86.3</v>
       </c>
       <c r="D4" t="n">
-        <v>79212029</v>
+        <v>63810284</v>
       </c>
       <c r="E4" t="n">
-        <v>-4.07</v>
-      </c>
-      <c r="F4" t="inlineStr"/>
+        <v>3.17</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>🔥爆升</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
@@ -547,18 +559,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>461.6</v>
+        <v>477.8</v>
       </c>
       <c r="D5" t="n">
-        <v>36237657</v>
+        <v>30823239</v>
       </c>
       <c r="E5" t="n">
-        <v>-4.63</v>
-      </c>
-      <c r="F5" t="inlineStr"/>
+        <v>3.51</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>🔥爆升</t>
+        </is>
+      </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
@@ -574,18 +590,18 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>88.7</v>
+        <v>90.15000000000001</v>
       </c>
       <c r="D6" t="n">
-        <v>26427225</v>
+        <v>18353594</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.47</v>
+        <v>1.63</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>
@@ -601,18 +617,18 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>156.9</v>
+        <v>157.8</v>
       </c>
       <c r="D7" t="n">
-        <v>17653835</v>
+        <v>12411214</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>0.57</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-20</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -466,22 +466,18 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8.65</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>370182314</v>
+        <v>242887354</v>
       </c>
       <c r="E2" t="n">
-        <v>4.34</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>🔥爆升</t>
-        </is>
-      </c>
+        <v>-1.27</v>
+      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -497,22 +493,18 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>27.74</v>
+        <v>27.42</v>
       </c>
       <c r="D3" t="n">
-        <v>167547503</v>
+        <v>158569507</v>
       </c>
       <c r="E3" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>🔥爆升</t>
-        </is>
-      </c>
+        <v>-1.15</v>
+      </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -528,22 +520,18 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>86.3</v>
+        <v>85.2</v>
       </c>
       <c r="D4" t="n">
-        <v>63810284</v>
+        <v>33366101</v>
       </c>
       <c r="E4" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>🔥爆升</t>
-        </is>
-      </c>
+        <v>-1.27</v>
+      </c>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -559,22 +547,18 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>477.8</v>
+        <v>474</v>
       </c>
       <c r="D5" t="n">
-        <v>30823239</v>
+        <v>21362880</v>
       </c>
       <c r="E5" t="n">
-        <v>3.51</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>🔥爆升</t>
-        </is>
-      </c>
+        <v>-0.8</v>
+      </c>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -590,18 +574,18 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>90.15000000000001</v>
+        <v>89.8</v>
       </c>
       <c r="D6" t="n">
-        <v>18353594</v>
+        <v>15912302</v>
       </c>
       <c r="E6" t="n">
-        <v>1.63</v>
+        <v>-0.39</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>
@@ -617,18 +601,18 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>157.8</v>
+        <v>156.5</v>
       </c>
       <c r="D7" t="n">
-        <v>12411214</v>
+        <v>9742490</v>
       </c>
       <c r="E7" t="n">
-        <v>0.57</v>
+        <v>-0.82</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -466,18 +466,18 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8.539999999999999</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>242887354</v>
+        <v>197219602</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.27</v>
+        <v>0.12</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -493,25 +493,25 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>27.42</v>
+        <v>26.68</v>
       </c>
       <c r="D3" t="n">
-        <v>158569507</v>
+        <v>147614646</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.15</v>
+        <v>-2.7</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3690.HK</t>
+          <t>0700.HK</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -520,25 +520,25 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>85.2</v>
+        <v>440.6</v>
       </c>
       <c r="D4" t="n">
-        <v>33366101</v>
+        <v>66379971</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.27</v>
+        <v>-7.05</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0700.HK</t>
+          <t>3690.HK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -547,18 +547,18 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>474</v>
+        <v>83.65000000000001</v>
       </c>
       <c r="D5" t="n">
-        <v>21362880</v>
+        <v>40536626</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.8</v>
+        <v>-1.82</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -574,18 +574,18 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>89.8</v>
+        <v>87.84999999999999</v>
       </c>
       <c r="D6" t="n">
-        <v>15912302</v>
+        <v>16178089</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.39</v>
+        <v>-2.17</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>
@@ -601,18 +601,18 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>156.5</v>
+        <v>158.9</v>
       </c>
       <c r="D7" t="n">
-        <v>9742490</v>
+        <v>14301334</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.82</v>
+        <v>1.53</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -466,18 +466,18 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8.550000000000001</v>
+        <v>8.74</v>
       </c>
       <c r="D2" t="n">
-        <v>197219602</v>
+        <v>232993324</v>
       </c>
       <c r="E2" t="n">
-        <v>0.12</v>
+        <v>2.22</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
     </row>
@@ -493,25 +493,25 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>26.68</v>
+        <v>27.14</v>
       </c>
       <c r="D3" t="n">
-        <v>147614646</v>
+        <v>87140868</v>
       </c>
       <c r="E3" t="n">
-        <v>-2.7</v>
+        <v>1.72</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0700.HK</t>
+          <t>3690.HK</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -520,25 +520,29 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>440.6</v>
+        <v>87.3</v>
       </c>
       <c r="D4" t="n">
-        <v>66379971</v>
+        <v>63252932</v>
       </c>
       <c r="E4" t="n">
-        <v>-7.05</v>
-      </c>
-      <c r="F4" t="inlineStr"/>
+        <v>4.36</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>🔥爆升</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3690.HK</t>
+          <t>0700.HK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -547,72 +551,72 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>83.65000000000001</v>
+        <v>445.2</v>
       </c>
       <c r="D5" t="n">
-        <v>40536626</v>
+        <v>22888928</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.82</v>
+        <v>1.04</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1211.HK</t>
+          <t>0005.HK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>新能源</t>
+          <t>銀行</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>87.84999999999999</v>
+        <v>161.5</v>
       </c>
       <c r="D6" t="n">
-        <v>16178089</v>
+        <v>16630615</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.17</v>
+        <v>1.64</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0005.HK</t>
+          <t>1211.HK</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>銀行</t>
+          <t>新能源</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>158.9</v>
+        <v>88.65000000000001</v>
       </c>
       <c r="D7" t="n">
-        <v>14301334</v>
+        <v>16430698</v>
       </c>
       <c r="E7" t="n">
-        <v>1.53</v>
+        <v>0.91</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -466,18 +466,18 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8.74</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>232993324</v>
+        <v>193006026</v>
       </c>
       <c r="E2" t="n">
-        <v>2.22</v>
+        <v>0.46</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
     </row>
@@ -493,18 +493,18 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>27.14</v>
+        <v>26.72</v>
       </c>
       <c r="D3" t="n">
-        <v>87140868</v>
+        <v>100081028</v>
       </c>
       <c r="E3" t="n">
-        <v>1.72</v>
+        <v>-1.55</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
     </row>
@@ -520,22 +520,18 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>87.3</v>
+        <v>86.7</v>
       </c>
       <c r="D4" t="n">
-        <v>63252932</v>
+        <v>32839785</v>
       </c>
       <c r="E4" t="n">
-        <v>4.36</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>🔥爆升</t>
-        </is>
-      </c>
+        <v>-0.6899999999999999</v>
+      </c>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
     </row>
@@ -551,72 +547,72 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>445.2</v>
+        <v>434.6</v>
       </c>
       <c r="D5" t="n">
-        <v>22888928</v>
+        <v>22960603</v>
       </c>
       <c r="E5" t="n">
-        <v>1.04</v>
+        <v>-2.38</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0005.HK</t>
+          <t>1211.HK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>銀行</t>
+          <t>新能源</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>161.5</v>
+        <v>88.65000000000001</v>
       </c>
       <c r="D6" t="n">
-        <v>16630615</v>
+        <v>13599908</v>
       </c>
       <c r="E6" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1211.HK</t>
+          <t>0005.HK</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>新能源</t>
+          <t>銀行</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>88.65000000000001</v>
+        <v>161.4</v>
       </c>
       <c r="D7" t="n">
-        <v>16430698</v>
+        <v>10607473</v>
       </c>
       <c r="E7" t="n">
-        <v>0.91</v>
+        <v>-0.06</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -469,7 +469,7 @@
         <v>8.779999999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>193006026</v>
+        <v>192790026</v>
       </c>
       <c r="E2" t="n">
         <v>0.46</v>
@@ -477,7 +477,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
     </row>
@@ -496,7 +496,7 @@
         <v>26.72</v>
       </c>
       <c r="D3" t="n">
-        <v>100081028</v>
+        <v>100009828</v>
       </c>
       <c r="E3" t="n">
         <v>-1.55</v>
@@ -504,7 +504,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
     </row>
@@ -523,7 +523,7 @@
         <v>86.7</v>
       </c>
       <c r="D4" t="n">
-        <v>32839785</v>
+        <v>32833485</v>
       </c>
       <c r="E4" t="n">
         <v>-0.6899999999999999</v>
@@ -531,7 +531,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
     </row>
@@ -550,7 +550,7 @@
         <v>434.6</v>
       </c>
       <c r="D5" t="n">
-        <v>22960603</v>
+        <v>22959603</v>
       </c>
       <c r="E5" t="n">
         <v>-2.38</v>
@@ -558,7 +558,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
         <v>88.65000000000001</v>
       </c>
       <c r="D6" t="n">
-        <v>13599908</v>
+        <v>13598408</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -585,7 +585,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
     </row>
@@ -604,7 +604,7 @@
         <v>161.4</v>
       </c>
       <c r="D7" t="n">
-        <v>10607473</v>
+        <v>10606273</v>
       </c>
       <c r="E7" t="n">
         <v>-0.06</v>
@@ -612,7 +612,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-25</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -477,7 +477,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -504,7 +504,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -531,7 +531,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -558,7 +558,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -585,7 +585,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>
@@ -612,7 +612,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-26</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -466,18 +466,18 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8.779999999999999</v>
+        <v>8.99</v>
       </c>
       <c r="D2" t="n">
-        <v>192790026</v>
+        <v>394625581</v>
       </c>
       <c r="E2" t="n">
-        <v>0.46</v>
+        <v>2.39</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -493,18 +493,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>26.72</v>
+        <v>28.68</v>
       </c>
       <c r="D3" t="n">
-        <v>100009828</v>
+        <v>274947607</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.55</v>
-      </c>
-      <c r="F3" t="inlineStr"/>
+        <v>7.34</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>🔥爆升</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -520,18 +524,18 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>86.7</v>
+        <v>89.3</v>
       </c>
       <c r="D4" t="n">
-        <v>32833485</v>
+        <v>65387089</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.6899999999999999</v>
+        <v>3</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
@@ -547,72 +551,72 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>434.6</v>
+        <v>443</v>
       </c>
       <c r="D5" t="n">
-        <v>22959603</v>
+        <v>14455552</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.38</v>
+        <v>1.93</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1211.HK</t>
+          <t>0005.HK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>新能源</t>
+          <t>銀行</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>88.65000000000001</v>
+        <v>162.8</v>
       </c>
       <c r="D6" t="n">
-        <v>13598408</v>
+        <v>12937563</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>0.87</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0005.HK</t>
+          <t>1211.HK</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>銀行</t>
+          <t>新能源</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>161.4</v>
+        <v>88.55</v>
       </c>
       <c r="D7" t="n">
-        <v>10606273</v>
+        <v>12447861</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.06</v>
+        <v>-0.11</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-27</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -466,18 +466,18 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8.99</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>394625581</v>
+        <v>521637128</v>
       </c>
       <c r="E2" t="n">
-        <v>2.39</v>
+        <v>1.56</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -493,22 +493,18 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>28.68</v>
+        <v>29.26</v>
       </c>
       <c r="D3" t="n">
-        <v>274947607</v>
+        <v>227304562</v>
       </c>
       <c r="E3" t="n">
-        <v>7.34</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>🔥爆升</t>
-        </is>
-      </c>
+        <v>2.02</v>
+      </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -524,18 +520,18 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>89.3</v>
+        <v>90.3</v>
       </c>
       <c r="D4" t="n">
-        <v>65387089</v>
+        <v>63694323</v>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>1.12</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
@@ -551,72 +547,72 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>443</v>
+        <v>447.2</v>
       </c>
       <c r="D5" t="n">
-        <v>14455552</v>
+        <v>18143997</v>
       </c>
       <c r="E5" t="n">
-        <v>1.93</v>
+        <v>0.95</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0005.HK</t>
+          <t>1211.HK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>銀行</t>
+          <t>新能源</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>162.8</v>
+        <v>89.8</v>
       </c>
       <c r="D6" t="n">
-        <v>12937563</v>
+        <v>15924123</v>
       </c>
       <c r="E6" t="n">
-        <v>0.87</v>
+        <v>1.41</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1211.HK</t>
+          <t>0005.HK</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>新能源</t>
+          <t>銀行</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>88.55</v>
+        <v>162</v>
       </c>
       <c r="D7" t="n">
-        <v>12447861</v>
+        <v>8011395</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.11</v>
+        <v>-0.49</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -457,54 +457,58 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0939.HK</t>
+          <t>1810.HK</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>銀行</t>
+          <t>科技</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>9.130000000000001</v>
+        <v>31.88</v>
       </c>
       <c r="D2" t="n">
-        <v>521637128</v>
+        <v>482249702</v>
       </c>
       <c r="E2" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="F2" t="inlineStr"/>
+        <v>8.949999999999999</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>🔥爆升</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1810.HK</t>
+          <t>0939.HK</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>科技</t>
+          <t>銀行</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>29.26</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="D3" t="n">
-        <v>227304562</v>
+        <v>394939486</v>
       </c>
       <c r="E3" t="n">
-        <v>2.02</v>
+        <v>0.88</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -520,18 +524,18 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>90.3</v>
+        <v>92.3</v>
       </c>
       <c r="D4" t="n">
-        <v>63694323</v>
+        <v>81345360</v>
       </c>
       <c r="E4" t="n">
-        <v>1.12</v>
+        <v>2.21</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -547,18 +551,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>447.2</v>
+        <v>466.4</v>
       </c>
       <c r="D5" t="n">
-        <v>18143997</v>
+        <v>36205493</v>
       </c>
       <c r="E5" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="F5" t="inlineStr"/>
+        <v>4.29</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>🔥爆升</t>
+        </is>
+      </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -574,18 +582,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>89.8</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="D6" t="n">
-        <v>15924123</v>
+        <v>35589277</v>
       </c>
       <c r="E6" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="F6" t="inlineStr"/>
+        <v>4.23</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>🔥爆升</t>
+        </is>
+      </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -601,18 +613,18 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>162</v>
+        <v>164.7</v>
       </c>
       <c r="D7" t="n">
-        <v>8011395</v>
+        <v>20529450</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.49</v>
+        <v>1.67</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -457,58 +457,54 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1810.HK</t>
+          <t>0939.HK</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>科技</t>
+          <t>銀行</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>31.88</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>482249702</v>
+        <v>400904777</v>
       </c>
       <c r="E2" t="n">
-        <v>8.949999999999999</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>🔥爆升</t>
-        </is>
-      </c>
+        <v>1.63</v>
+      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0939.HK</t>
+          <t>1810.HK</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>銀行</t>
+          <t>科技</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>9.210000000000001</v>
+        <v>31.04</v>
       </c>
       <c r="D3" t="n">
-        <v>394939486</v>
+        <v>242298626</v>
       </c>
       <c r="E3" t="n">
-        <v>0.88</v>
+        <v>-2.63</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -524,18 +520,18 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>92.3</v>
+        <v>92.65000000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>81345360</v>
+        <v>50353985</v>
       </c>
       <c r="E4" t="n">
-        <v>2.21</v>
+        <v>0.38</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -551,22 +547,18 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>466.4</v>
+        <v>471.8</v>
       </c>
       <c r="D5" t="n">
-        <v>36205493</v>
+        <v>31792979</v>
       </c>
       <c r="E5" t="n">
-        <v>4.29</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>🔥爆升</t>
-        </is>
-      </c>
+        <v>1.16</v>
+      </c>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -582,22 +574,18 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>93.59999999999999</v>
+        <v>94.8</v>
       </c>
       <c r="D6" t="n">
-        <v>35589277</v>
+        <v>26511489</v>
       </c>
       <c r="E6" t="n">
-        <v>4.23</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>🔥爆升</t>
-        </is>
-      </c>
+        <v>1.28</v>
+      </c>
+      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>
@@ -613,18 +601,18 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>164.7</v>
+        <v>164.5</v>
       </c>
       <c r="D7" t="n">
-        <v>20529450</v>
+        <v>21290781</v>
       </c>
       <c r="E7" t="n">
-        <v>1.67</v>
+        <v>-0.12</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -457,54 +457,54 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0939.HK</t>
+          <t>1810.HK</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>銀行</t>
+          <t>科技</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>9.359999999999999</v>
+        <v>28.78</v>
       </c>
       <c r="D2" t="n">
-        <v>400904777</v>
+        <v>414222966</v>
       </c>
       <c r="E2" t="n">
-        <v>1.63</v>
+        <v>-7.28</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1810.HK</t>
+          <t>0939.HK</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>科技</t>
+          <t>銀行</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>31.04</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="D3" t="n">
-        <v>242298626</v>
+        <v>289828983</v>
       </c>
       <c r="E3" t="n">
-        <v>-2.63</v>
+        <v>-1.6</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>
@@ -520,18 +520,18 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>92.65000000000001</v>
+        <v>92.5</v>
       </c>
       <c r="D4" t="n">
-        <v>50353985</v>
+        <v>50465400</v>
       </c>
       <c r="E4" t="n">
-        <v>0.38</v>
+        <v>-0.16</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>
@@ -547,18 +547,18 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>471.8</v>
+        <v>475.2</v>
       </c>
       <c r="D5" t="n">
-        <v>31792979</v>
+        <v>31101240</v>
       </c>
       <c r="E5" t="n">
-        <v>1.16</v>
+        <v>0.72</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>
@@ -574,18 +574,18 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>94.8</v>
+        <v>94.15000000000001</v>
       </c>
       <c r="D6" t="n">
-        <v>26511489</v>
+        <v>27657478</v>
       </c>
       <c r="E6" t="n">
-        <v>1.28</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>
@@ -601,18 +601,18 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>164.5</v>
+        <v>168.2</v>
       </c>
       <c r="D7" t="n">
-        <v>21290781</v>
+        <v>21452178</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.12</v>
+        <v>2.25</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -469,7 +469,7 @@
         <v>28.78</v>
       </c>
       <c r="D2" t="n">
-        <v>414222966</v>
+        <v>414222166</v>
       </c>
       <c r="E2" t="n">
         <v>-7.28</v>
@@ -477,7 +477,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
@@ -496,7 +496,7 @@
         <v>9.210000000000001</v>
       </c>
       <c r="D3" t="n">
-        <v>289828983</v>
+        <v>289808983</v>
       </c>
       <c r="E3" t="n">
         <v>-1.6</v>
@@ -504,7 +504,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
@@ -523,7 +523,7 @@
         <v>92.5</v>
       </c>
       <c r="D4" t="n">
-        <v>50465400</v>
+        <v>50464900</v>
       </c>
       <c r="E4" t="n">
         <v>-0.16</v>
@@ -531,7 +531,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
@@ -550,7 +550,7 @@
         <v>475.2</v>
       </c>
       <c r="D5" t="n">
-        <v>31101240</v>
+        <v>31100240</v>
       </c>
       <c r="E5" t="n">
         <v>0.72</v>
@@ -558,7 +558,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
         <v>94.15000000000001</v>
       </c>
       <c r="D6" t="n">
-        <v>27657478</v>
+        <v>27656478</v>
       </c>
       <c r="E6" t="n">
         <v>-0.6899999999999999</v>
@@ -585,7 +585,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
@@ -604,7 +604,7 @@
         <v>168.2</v>
       </c>
       <c r="D7" t="n">
-        <v>21452178</v>
+        <v>21451778</v>
       </c>
       <c r="E7" t="n">
         <v>2.25</v>
@@ -612,7 +612,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -477,7 +477,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
     </row>
@@ -504,7 +504,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
     </row>
@@ -531,7 +531,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
     </row>
@@ -558,7 +558,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
     </row>
@@ -585,7 +585,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
     </row>
@@ -612,7 +612,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -466,18 +466,18 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>28.78</v>
+        <v>27.96</v>
       </c>
       <c r="D2" t="n">
-        <v>414222166</v>
+        <v>291271651</v>
       </c>
       <c r="E2" t="n">
-        <v>-7.28</v>
+        <v>-2.85</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -493,18 +493,18 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>9.210000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="D3" t="n">
-        <v>289808983</v>
+        <v>197134261</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.6</v>
+        <v>-0.11</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -520,18 +520,18 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>92.5</v>
+        <v>93.45</v>
       </c>
       <c r="D4" t="n">
-        <v>50464900</v>
+        <v>39105288</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.16</v>
+        <v>1.03</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -547,18 +547,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>475.2</v>
+        <v>490.4</v>
       </c>
       <c r="D5" t="n">
-        <v>31100240</v>
+        <v>38650010</v>
       </c>
       <c r="E5" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="F5" t="inlineStr"/>
+        <v>3.2</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>🔥爆升</t>
+        </is>
+      </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -574,18 +578,18 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>94.15000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="D6" t="n">
-        <v>27656478</v>
+        <v>17730091</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.6899999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>
@@ -604,15 +608,15 @@
         <v>168.2</v>
       </c>
       <c r="D7" t="n">
-        <v>21451778</v>
+        <v>12417942</v>
       </c>
       <c r="E7" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-03</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -457,54 +457,54 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1810.HK</t>
+          <t>0939.HK</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>科技</t>
+          <t>銀行</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>27.96</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>291271651</v>
+        <v>292789577</v>
       </c>
       <c r="E2" t="n">
-        <v>-2.85</v>
+        <v>-3.37</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0939.HK</t>
+          <t>1810.HK</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>銀行</t>
+          <t>科技</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>9.199999999999999</v>
+        <v>27.96</v>
       </c>
       <c r="D3" t="n">
-        <v>197134261</v>
+        <v>154556311</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.11</v>
+        <v>0</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
     </row>
@@ -520,103 +520,99 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>93.45</v>
+        <v>92.7</v>
       </c>
       <c r="D4" t="n">
-        <v>39105288</v>
+        <v>45158770</v>
       </c>
       <c r="E4" t="n">
-        <v>1.03</v>
+        <v>-0.8</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0700.HK</t>
+          <t>0005.HK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>科技</t>
+          <t>銀行</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>490.4</v>
+        <v>166.5</v>
       </c>
       <c r="D5" t="n">
-        <v>38650010</v>
+        <v>27431403</v>
       </c>
       <c r="E5" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>🔥爆升</t>
-        </is>
-      </c>
+        <v>-1.01</v>
+      </c>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1211.HK</t>
+          <t>0700.HK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>新能源</t>
+          <t>科技</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>94.90000000000001</v>
+        <v>487.6</v>
       </c>
       <c r="D6" t="n">
-        <v>17730091</v>
+        <v>24860119</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8</v>
+        <v>-0.57</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0005.HK</t>
+          <t>1211.HK</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>銀行</t>
+          <t>新能源</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>168.2</v>
+        <v>93.45</v>
       </c>
       <c r="D7" t="n">
-        <v>12417942</v>
+        <v>13395026</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>-1.53</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -466,18 +466,18 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8.890000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>292789577</v>
+        <v>248228281</v>
       </c>
       <c r="E2" t="n">
-        <v>-3.37</v>
+        <v>-1.01</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
     </row>
@@ -493,18 +493,18 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>27.96</v>
+        <v>27.64</v>
       </c>
       <c r="D3" t="n">
-        <v>154556311</v>
+        <v>140378892</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>-1.14</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
     </row>
@@ -520,72 +520,72 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>92.7</v>
+        <v>93.05</v>
       </c>
       <c r="D4" t="n">
-        <v>45158770</v>
+        <v>39990799</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.8</v>
+        <v>0.38</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0005.HK</t>
+          <t>0700.HK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>銀行</t>
+          <t>科技</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>166.5</v>
+        <v>492.2</v>
       </c>
       <c r="D5" t="n">
-        <v>27431403</v>
+        <v>25662578</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.01</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0700.HK</t>
+          <t>0005.HK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>科技</t>
+          <t>銀行</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>487.6</v>
+        <v>162.1</v>
       </c>
       <c r="D6" t="n">
-        <v>24860119</v>
+        <v>23151026</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.57</v>
+        <v>-2.64</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
     </row>
@@ -601,18 +601,18 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>93.45</v>
+        <v>93.8</v>
       </c>
       <c r="D7" t="n">
-        <v>13395026</v>
+        <v>15747198</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.53</v>
+        <v>0.37</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -466,18 +466,18 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8.800000000000001</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>248228281</v>
+        <v>208085592</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.01</v>
+        <v>0.68</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
@@ -493,52 +493,52 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>27.64</v>
+        <v>26.86</v>
       </c>
       <c r="D3" t="n">
-        <v>140378892</v>
+        <v>171820604</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.14</v>
+        <v>-2.82</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3690.HK</t>
+          <t>1211.HK</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>科技</t>
+          <t>新能源</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>93.05</v>
+        <v>89.84999999999999</v>
       </c>
       <c r="D4" t="n">
-        <v>39990799</v>
+        <v>23763601</v>
       </c>
       <c r="E4" t="n">
-        <v>0.38</v>
+        <v>-4.21</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0700.HK</t>
+          <t>3690.HK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -547,72 +547,72 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>492.2</v>
+        <v>92</v>
       </c>
       <c r="D5" t="n">
-        <v>25662578</v>
+        <v>21474225</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9399999999999999</v>
+        <v>-1.13</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0005.HK</t>
+          <t>0700.HK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>銀行</t>
+          <t>科技</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>162.1</v>
+        <v>480.4</v>
       </c>
       <c r="D6" t="n">
-        <v>23151026</v>
+        <v>17740398</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.64</v>
+        <v>-2.4</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1211.HK</t>
+          <t>0005.HK</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>新能源</t>
+          <t>銀行</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>93.8</v>
+        <v>159.5</v>
       </c>
       <c r="D7" t="n">
-        <v>15747198</v>
+        <v>16870539</v>
       </c>
       <c r="E7" t="n">
-        <v>0.37</v>
+        <v>-1.6</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -466,18 +466,18 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8.859999999999999</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>208085592</v>
+        <v>177249304</v>
       </c>
       <c r="E2" t="n">
-        <v>0.68</v>
+        <v>-0.79</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -493,52 +493,52 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>26.86</v>
+        <v>27.06</v>
       </c>
       <c r="D3" t="n">
-        <v>171820604</v>
+        <v>148234531</v>
       </c>
       <c r="E3" t="n">
-        <v>-2.82</v>
+        <v>0.74</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1211.HK</t>
+          <t>3690.HK</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>新能源</t>
+          <t>科技</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>89.84999999999999</v>
+        <v>92.2</v>
       </c>
       <c r="D4" t="n">
-        <v>23763601</v>
+        <v>28419307</v>
       </c>
       <c r="E4" t="n">
-        <v>-4.21</v>
+        <v>0</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3690.HK</t>
+          <t>0700.HK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -547,45 +547,45 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>92</v>
+        <v>478.8</v>
       </c>
       <c r="D5" t="n">
-        <v>21474225</v>
+        <v>16320039</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.13</v>
+        <v>-0.08</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0700.HK</t>
+          <t>1211.HK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>科技</t>
+          <t>新能源</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>480.4</v>
+        <v>90.15000000000001</v>
       </c>
       <c r="D6" t="n">
-        <v>17740398</v>
+        <v>14669577</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.4</v>
+        <v>0.33</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>
@@ -601,18 +601,18 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>159.5</v>
+        <v>161.2</v>
       </c>
       <c r="D7" t="n">
-        <v>16870539</v>
+        <v>11751047</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.6</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -469,7 +469,7 @@
         <v>8.789999999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>177249304</v>
+        <v>177039304</v>
       </c>
       <c r="E2" t="n">
         <v>-0.79</v>
@@ -477,7 +477,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
     </row>
@@ -496,7 +496,7 @@
         <v>27.06</v>
       </c>
       <c r="D3" t="n">
-        <v>148234531</v>
+        <v>148233931</v>
       </c>
       <c r="E3" t="n">
         <v>0.74</v>
@@ -504,7 +504,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
     </row>
@@ -523,7 +523,7 @@
         <v>92.2</v>
       </c>
       <c r="D4" t="n">
-        <v>28419307</v>
+        <v>28419007</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -531,7 +531,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
     </row>
@@ -550,7 +550,7 @@
         <v>478.8</v>
       </c>
       <c r="D5" t="n">
-        <v>16320039</v>
+        <v>16319939</v>
       </c>
       <c r="E5" t="n">
         <v>-0.08</v>
@@ -558,7 +558,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
         <v>90.15000000000001</v>
       </c>
       <c r="D6" t="n">
-        <v>14669577</v>
+        <v>14668177</v>
       </c>
       <c r="E6" t="n">
         <v>0.33</v>
@@ -585,7 +585,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
     </row>
@@ -604,7 +604,7 @@
         <v>161.2</v>
       </c>
       <c r="D7" t="n">
-        <v>11751047</v>
+        <v>11750647</v>
       </c>
       <c r="E7" t="n">
         <v>0.6899999999999999</v>
@@ -612,7 +612,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -477,7 +477,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
@@ -504,7 +504,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
@@ -531,7 +531,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
@@ -558,7 +558,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
@@ -585,7 +585,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
@@ -612,7 +612,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -457,46 +457,46 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0939.HK</t>
+          <t>1810.HK</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>銀行</t>
+          <t>科技</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8.789999999999999</v>
+        <v>27.62</v>
       </c>
       <c r="D2" t="n">
-        <v>177039304</v>
+        <v>149703382</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.79</v>
+        <v>2.07</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1810.HK</t>
+          <t>0939.HK</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>科技</t>
+          <t>銀行</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>27.06</v>
+        <v>8.85</v>
       </c>
       <c r="D3" t="n">
-        <v>148233931</v>
+        <v>131565154</v>
       </c>
       <c r="E3" t="n">
         <v>0.74</v>
@@ -504,7 +504,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
@@ -520,18 +520,18 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>92.2</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>28419007</v>
+        <v>25201862</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
@@ -547,18 +547,18 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>478.8</v>
+        <v>481.4</v>
       </c>
       <c r="D5" t="n">
-        <v>16319939</v>
+        <v>15509424</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.08</v>
+        <v>0.54</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
@@ -574,18 +574,18 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>90.15000000000001</v>
+        <v>92.3</v>
       </c>
       <c r="D6" t="n">
-        <v>14668177</v>
+        <v>11304355</v>
       </c>
       <c r="E6" t="n">
-        <v>0.33</v>
+        <v>2.38</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
@@ -601,18 +601,18 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>161.2</v>
+        <v>162.5</v>
       </c>
       <c r="D7" t="n">
-        <v>11750647</v>
+        <v>8270403</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -457,54 +457,54 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1810.HK</t>
+          <t>0939.HK</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>科技</t>
+          <t>銀行</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>27.62</v>
+        <v>8.82</v>
       </c>
       <c r="D2" t="n">
-        <v>149703382</v>
+        <v>126200991</v>
       </c>
       <c r="E2" t="n">
-        <v>2.07</v>
+        <v>-0.34</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0939.HK</t>
+          <t>1810.HK</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>銀行</t>
+          <t>科技</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>8.85</v>
+        <v>26.66</v>
       </c>
       <c r="D3" t="n">
-        <v>131565154</v>
+        <v>120335668</v>
       </c>
       <c r="E3" t="n">
-        <v>0.74</v>
+        <v>-3.48</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -520,18 +520,18 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>93.90000000000001</v>
+        <v>93.05</v>
       </c>
       <c r="D4" t="n">
-        <v>25201862</v>
+        <v>33421904</v>
       </c>
       <c r="E4" t="n">
-        <v>1.84</v>
+        <v>-0.91</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -547,18 +547,18 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>481.4</v>
+        <v>470.8</v>
       </c>
       <c r="D5" t="n">
-        <v>15509424</v>
+        <v>19558379</v>
       </c>
       <c r="E5" t="n">
-        <v>0.54</v>
+        <v>-2.2</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -574,18 +574,18 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>92.3</v>
+        <v>89.7</v>
       </c>
       <c r="D6" t="n">
-        <v>11304355</v>
+        <v>9910609</v>
       </c>
       <c r="E6" t="n">
-        <v>2.38</v>
+        <v>-2.82</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -601,18 +601,18 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>162.5</v>
+        <v>161.7</v>
       </c>
       <c r="D7" t="n">
-        <v>8270403</v>
+        <v>9780226</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8100000000000001</v>
+        <v>-0.49</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -466,18 +466,18 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8.82</v>
+        <v>8.75</v>
       </c>
       <c r="D2" t="n">
-        <v>126200991</v>
+        <v>113806045</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.34</v>
+        <v>-0.85</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
@@ -493,18 +493,18 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>26.66</v>
+        <v>26.36</v>
       </c>
       <c r="D3" t="n">
-        <v>120335668</v>
+        <v>106976643</v>
       </c>
       <c r="E3" t="n">
-        <v>-3.48</v>
+        <v>-1.13</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
@@ -520,18 +520,18 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>93.05</v>
+        <v>91.65000000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>33421904</v>
+        <v>33457066</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.91</v>
+        <v>-1.5</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
@@ -547,18 +547,18 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>470.8</v>
+        <v>461.6</v>
       </c>
       <c r="D5" t="n">
-        <v>19558379</v>
+        <v>27596615</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.2</v>
+        <v>-1.95</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
@@ -574,18 +574,18 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>89.7</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="D6" t="n">
-        <v>9910609</v>
+        <v>10269062</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.82</v>
+        <v>-0.11</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
@@ -601,18 +601,18 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>161.7</v>
+        <v>161.4</v>
       </c>
       <c r="D7" t="n">
-        <v>9780226</v>
+        <v>7210163</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.49</v>
+        <v>-0.19</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -466,18 +466,18 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8.75</v>
+        <v>8.82</v>
       </c>
       <c r="D2" t="n">
-        <v>113806045</v>
+        <v>149564111</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.85</v>
+        <v>0.86</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -493,25 +493,25 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>26.36</v>
+        <v>25.88</v>
       </c>
       <c r="D3" t="n">
-        <v>106976643</v>
+        <v>116429640</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.13</v>
+        <v>-1.82</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3690.HK</t>
+          <t>0700.HK</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -520,25 +520,25 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>91.65000000000001</v>
+        <v>441</v>
       </c>
       <c r="D4" t="n">
-        <v>33457066</v>
+        <v>66424723</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.5</v>
+        <v>-4.46</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0700.HK</t>
+          <t>3690.HK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -547,18 +547,18 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>461.6</v>
+        <v>91.25</v>
       </c>
       <c r="D5" t="n">
-        <v>27596615</v>
+        <v>21499871</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.95</v>
+        <v>-0.44</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -574,18 +574,18 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>89.59999999999999</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="D6" t="n">
-        <v>10269062</v>
+        <v>11982274</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.11</v>
+        <v>-1.34</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -601,18 +601,18 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>161.4</v>
+        <v>163</v>
       </c>
       <c r="D7" t="n">
-        <v>7210163</v>
+        <v>7978564</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.19</v>
+        <v>1.05</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Top Stocks" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Sector Analysis" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Top Stocks" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sector Analysis" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -466,18 +466,18 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8.82</v>
+        <v>8.74</v>
       </c>
       <c r="D2" t="n">
-        <v>149564111</v>
+        <v>137133813</v>
       </c>
       <c r="E2" t="n">
-        <v>0.86</v>
+        <v>-0.96</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
@@ -493,25 +493,25 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>25.88</v>
+        <v>25.62</v>
       </c>
       <c r="D3" t="n">
-        <v>116429640</v>
+        <v>91057676</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.82</v>
+        <v>-1</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0700.HK</t>
+          <t>3690.HK</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -520,25 +520,25 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>441</v>
+        <v>87.2</v>
       </c>
       <c r="D4" t="n">
-        <v>66424723</v>
+        <v>75329530</v>
       </c>
       <c r="E4" t="n">
-        <v>-4.46</v>
+        <v>-4.44</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3690.HK</t>
+          <t>0700.HK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -547,18 +547,18 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>91.25</v>
+        <v>440</v>
       </c>
       <c r="D5" t="n">
-        <v>21499871</v>
+        <v>30601160</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.44</v>
+        <v>-0.23</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
@@ -574,18 +574,18 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>88.40000000000001</v>
+        <v>88.25</v>
       </c>
       <c r="D6" t="n">
-        <v>11982274</v>
+        <v>11917806</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.34</v>
+        <v>-0.17</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
@@ -601,18 +601,18 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>163</v>
+        <v>160.8</v>
       </c>
       <c r="D7" t="n">
-        <v>7978564</v>
+        <v>6738838</v>
       </c>
       <c r="E7" t="n">
-        <v>1.05</v>
+        <v>-1.35</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -469,7 +469,7 @@
         <v>8.74</v>
       </c>
       <c r="D2" t="n">
-        <v>137133813</v>
+        <v>137015813</v>
       </c>
       <c r="E2" t="n">
         <v>-0.96</v>
@@ -477,7 +477,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -496,7 +496,7 @@
         <v>25.62</v>
       </c>
       <c r="D3" t="n">
-        <v>91057676</v>
+        <v>91055676</v>
       </c>
       <c r="E3" t="n">
         <v>-1</v>
@@ -504,7 +504,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -523,7 +523,7 @@
         <v>87.2</v>
       </c>
       <c r="D4" t="n">
-        <v>75329530</v>
+        <v>75329330</v>
       </c>
       <c r="E4" t="n">
         <v>-4.44</v>
@@ -531,7 +531,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -550,7 +550,7 @@
         <v>440</v>
       </c>
       <c r="D5" t="n">
-        <v>30601160</v>
+        <v>30601060</v>
       </c>
       <c r="E5" t="n">
         <v>-0.23</v>
@@ -558,7 +558,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
         <v>88.25</v>
       </c>
       <c r="D6" t="n">
-        <v>11917806</v>
+        <v>11917106</v>
       </c>
       <c r="E6" t="n">
         <v>-0.17</v>
@@ -585,7 +585,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -604,7 +604,7 @@
         <v>160.8</v>
       </c>
       <c r="D7" t="n">
-        <v>6738838</v>
+        <v>6724838</v>
       </c>
       <c r="E7" t="n">
         <v>-1.35</v>
@@ -612,7 +612,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -477,7 +477,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -504,7 +504,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -531,7 +531,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -558,7 +558,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -585,7 +585,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -612,7 +612,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -466,18 +466,18 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8.74</v>
+        <v>8.9</v>
       </c>
       <c r="D2" t="n">
-        <v>137015813</v>
+        <v>164144134</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.96</v>
+        <v>1.83</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -493,18 +493,18 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>25.62</v>
+        <v>25.88</v>
       </c>
       <c r="D3" t="n">
-        <v>91055676</v>
+        <v>100097535</v>
       </c>
       <c r="E3" t="n">
-        <v>-1</v>
+        <v>1.01</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -520,18 +520,18 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>87.2</v>
+        <v>87.65000000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>75329330</v>
+        <v>26917511</v>
       </c>
       <c r="E4" t="n">
-        <v>-4.44</v>
+        <v>0.52</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -547,18 +547,18 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>440</v>
+        <v>446.4</v>
       </c>
       <c r="D5" t="n">
-        <v>30601060</v>
+        <v>19839108</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.23</v>
+        <v>1.45</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -574,18 +574,18 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>88.25</v>
+        <v>90.05</v>
       </c>
       <c r="D6" t="n">
-        <v>11917106</v>
+        <v>12868474</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.17</v>
+        <v>2.04</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -601,18 +601,18 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>160.8</v>
+        <v>163.5</v>
       </c>
       <c r="D7" t="n">
-        <v>6724838</v>
+        <v>7607874</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.35</v>
+        <v>1.68</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -457,54 +457,54 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0939.HK</t>
+          <t>1810.HK</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>銀行</t>
+          <t>科技</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8.9</v>
+        <v>26.18</v>
       </c>
       <c r="D2" t="n">
-        <v>164144134</v>
+        <v>179217411</v>
       </c>
       <c r="E2" t="n">
-        <v>1.83</v>
+        <v>1.16</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1810.HK</t>
+          <t>0939.HK</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>科技</t>
+          <t>銀行</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>25.88</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="D3" t="n">
-        <v>100097535</v>
+        <v>171072452</v>
       </c>
       <c r="E3" t="n">
-        <v>1.01</v>
+        <v>0.67</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
@@ -520,18 +520,18 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>87.65000000000001</v>
+        <v>85.55</v>
       </c>
       <c r="D4" t="n">
-        <v>26917511</v>
+        <v>52934212</v>
       </c>
       <c r="E4" t="n">
-        <v>0.52</v>
+        <v>-2.4</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
@@ -547,18 +547,18 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>446.4</v>
+        <v>442.4</v>
       </c>
       <c r="D5" t="n">
-        <v>19839108</v>
+        <v>23220078</v>
       </c>
       <c r="E5" t="n">
-        <v>1.45</v>
+        <v>-0.9</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
@@ -574,18 +574,18 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>90.05</v>
+        <v>90</v>
       </c>
       <c r="D6" t="n">
-        <v>12868474</v>
+        <v>12299489</v>
       </c>
       <c r="E6" t="n">
-        <v>2.04</v>
+        <v>-0.06</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
@@ -601,18 +601,18 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>163.5</v>
+        <v>162.1</v>
       </c>
       <c r="D7" t="n">
-        <v>7607874</v>
+        <v>5726985</v>
       </c>
       <c r="E7" t="n">
-        <v>1.68</v>
+        <v>-0.86</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -466,18 +466,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>26.18</v>
+        <v>27.44</v>
       </c>
       <c r="D2" t="n">
-        <v>179217411</v>
+        <v>339876011</v>
       </c>
       <c r="E2" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="F2" t="inlineStr"/>
+        <v>4.81</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>🔥爆升</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
@@ -493,18 +497,18 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>8.960000000000001</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="D3" t="n">
-        <v>171072452</v>
+        <v>187891158</v>
       </c>
       <c r="E3" t="n">
-        <v>0.67</v>
+        <v>1</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
@@ -520,18 +524,18 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>85.55</v>
+        <v>87.05</v>
       </c>
       <c r="D4" t="n">
-        <v>52934212</v>
+        <v>36758866</v>
       </c>
       <c r="E4" t="n">
-        <v>-2.4</v>
+        <v>1.75</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
@@ -547,18 +551,18 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>442.4</v>
+        <v>447.2</v>
       </c>
       <c r="D5" t="n">
-        <v>23220078</v>
+        <v>19774087</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.9</v>
+        <v>1.08</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
@@ -574,18 +578,18 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>90</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="D6" t="n">
-        <v>12299489</v>
+        <v>9395361</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.06</v>
+        <v>-0.67</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
@@ -601,18 +605,18 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>162.1</v>
+        <v>161.2</v>
       </c>
       <c r="D7" t="n">
-        <v>5726985</v>
+        <v>8433659</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.86</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -457,58 +457,54 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1810.HK</t>
+          <t>0939.HK</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>科技</t>
+          <t>銀行</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>27.44</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>339876011</v>
+        <v>237945061</v>
       </c>
       <c r="E2" t="n">
-        <v>4.81</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>🔥爆升</t>
-        </is>
-      </c>
+        <v>1.66</v>
+      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0939.HK</t>
+          <t>1810.HK</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>銀行</t>
+          <t>科技</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>9.050000000000001</v>
+        <v>27.76</v>
       </c>
       <c r="D3" t="n">
-        <v>187891158</v>
+        <v>178685584</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
@@ -524,18 +520,18 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>87.05</v>
+        <v>85.84999999999999</v>
       </c>
       <c r="D4" t="n">
-        <v>36758866</v>
+        <v>28598952</v>
       </c>
       <c r="E4" t="n">
-        <v>1.75</v>
+        <v>-1.38</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
@@ -551,18 +547,18 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>447.2</v>
+        <v>451.4</v>
       </c>
       <c r="D5" t="n">
-        <v>19774087</v>
+        <v>19622598</v>
       </c>
       <c r="E5" t="n">
-        <v>1.08</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
@@ -578,18 +574,18 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>89.40000000000001</v>
+        <v>91.8</v>
       </c>
       <c r="D6" t="n">
-        <v>9395361</v>
+        <v>14725223</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.67</v>
+        <v>2.68</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
@@ -605,10 +601,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>161.2</v>
+        <v>160.3</v>
       </c>
       <c r="D7" t="n">
-        <v>8433659</v>
+        <v>9509222</v>
       </c>
       <c r="E7" t="n">
         <v>-0.5600000000000001</v>
@@ -616,7 +612,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -466,18 +466,18 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>9.199999999999999</v>
+        <v>9.24</v>
       </c>
       <c r="D2" t="n">
-        <v>237945061</v>
+        <v>238011878</v>
       </c>
       <c r="E2" t="n">
-        <v>1.66</v>
+        <v>0.49</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
@@ -493,18 +493,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>27.76</v>
+        <v>29.02</v>
       </c>
       <c r="D3" t="n">
-        <v>178685584</v>
+        <v>180386553</v>
       </c>
       <c r="E3" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="F3" t="inlineStr"/>
+        <v>4.54</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>🔥爆升</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
@@ -520,18 +524,18 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>85.84999999999999</v>
+        <v>85</v>
       </c>
       <c r="D4" t="n">
-        <v>28598952</v>
+        <v>42941090</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.38</v>
+        <v>-0.99</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
@@ -547,18 +551,18 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>451.4</v>
+        <v>457</v>
       </c>
       <c r="D5" t="n">
-        <v>19622598</v>
+        <v>22327006</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.24</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
@@ -574,18 +578,18 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>91.8</v>
+        <v>93.15000000000001</v>
       </c>
       <c r="D6" t="n">
-        <v>14725223</v>
+        <v>14351523</v>
       </c>
       <c r="E6" t="n">
-        <v>2.68</v>
+        <v>1.47</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
@@ -601,18 +605,18 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>160.3</v>
+        <v>162.9</v>
       </c>
       <c r="D7" t="n">
-        <v>9509222</v>
+        <v>11361151</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.5600000000000001</v>
+        <v>1.62</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -469,7 +469,7 @@
         <v>9.24</v>
       </c>
       <c r="D2" t="n">
-        <v>238011878</v>
+        <v>238009878</v>
       </c>
       <c r="E2" t="n">
         <v>0.49</v>
@@ -477,7 +477,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -496,7 +496,7 @@
         <v>29.02</v>
       </c>
       <c r="D3" t="n">
-        <v>180386553</v>
+        <v>180377953</v>
       </c>
       <c r="E3" t="n">
         <v>4.54</v>
@@ -508,7 +508,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -527,7 +527,7 @@
         <v>85</v>
       </c>
       <c r="D4" t="n">
-        <v>42941090</v>
+        <v>42935990</v>
       </c>
       <c r="E4" t="n">
         <v>-0.99</v>
@@ -535,7 +535,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -554,7 +554,7 @@
         <v>457</v>
       </c>
       <c r="D5" t="n">
-        <v>22327006</v>
+        <v>22326906</v>
       </c>
       <c r="E5" t="n">
         <v>1.24</v>
@@ -562,7 +562,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -581,7 +581,7 @@
         <v>93.15000000000001</v>
       </c>
       <c r="D6" t="n">
-        <v>14351523</v>
+        <v>14344823</v>
       </c>
       <c r="E6" t="n">
         <v>1.47</v>
@@ -589,7 +589,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -608,7 +608,7 @@
         <v>162.9</v>
       </c>
       <c r="D7" t="n">
-        <v>11361151</v>
+        <v>11360351</v>
       </c>
       <c r="E7" t="n">
         <v>1.62</v>
@@ -616,7 +616,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -477,7 +477,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
@@ -535,7 +535,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
@@ -562,7 +562,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
@@ -589,7 +589,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
@@ -616,7 +616,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -466,18 +466,18 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>9.24</v>
+        <v>9.18</v>
       </c>
       <c r="D2" t="n">
-        <v>238009878</v>
+        <v>239550549</v>
       </c>
       <c r="E2" t="n">
-        <v>0.49</v>
+        <v>-0.76</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -493,22 +493,18 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>29.02</v>
+        <v>27.82</v>
       </c>
       <c r="D3" t="n">
-        <v>180377953</v>
+        <v>158055822</v>
       </c>
       <c r="E3" t="n">
-        <v>4.54</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>🔥爆升</t>
-        </is>
-      </c>
+        <v>-4.14</v>
+      </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -524,18 +520,18 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>85</v>
+        <v>82.7</v>
       </c>
       <c r="D4" t="n">
-        <v>42935990</v>
+        <v>45981032</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.99</v>
+        <v>-2.71</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -551,18 +547,18 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>457</v>
+        <v>440</v>
       </c>
       <c r="D5" t="n">
-        <v>22326906</v>
+        <v>29180102</v>
       </c>
       <c r="E5" t="n">
-        <v>1.24</v>
+        <v>-3.72</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -578,18 +574,18 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>93.15000000000001</v>
+        <v>92.8</v>
       </c>
       <c r="D6" t="n">
-        <v>14344823</v>
+        <v>18188585</v>
       </c>
       <c r="E6" t="n">
-        <v>1.47</v>
+        <v>-0.38</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
@@ -605,18 +601,18 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>162.9</v>
+        <v>161.5</v>
       </c>
       <c r="D7" t="n">
-        <v>11360351</v>
+        <v>10631099</v>
       </c>
       <c r="E7" t="n">
-        <v>1.62</v>
+        <v>-0.86</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -469,22 +469,22 @@
         <v>9.18</v>
       </c>
       <c r="D2" t="n">
-        <v>239550549</v>
+        <v>192122330</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.76</v>
+        <v>0.05</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1810.HK</t>
+          <t>3690.HK</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -493,25 +493,25 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>27.82</v>
+        <v>77.2</v>
       </c>
       <c r="D3" t="n">
-        <v>158055822</v>
+        <v>91023973</v>
       </c>
       <c r="E3" t="n">
-        <v>-4.14</v>
+        <v>-6.65</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3690.HK</t>
+          <t>1810.HK</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -520,72 +520,72 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>82.7</v>
+        <v>27.76</v>
       </c>
       <c r="D4" t="n">
-        <v>45981032</v>
+        <v>81490138</v>
       </c>
       <c r="E4" t="n">
-        <v>-2.71</v>
+        <v>-0.22</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0700.HK</t>
+          <t>1211.HK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>科技</t>
+          <t>新能源</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>440</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>29180102</v>
+        <v>19581215</v>
       </c>
       <c r="E5" t="n">
-        <v>-3.72</v>
+        <v>0.86</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1211.HK</t>
+          <t>0700.HK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>新能源</t>
+          <t>科技</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>92.8</v>
+        <v>442</v>
       </c>
       <c r="D6" t="n">
-        <v>18188585</v>
+        <v>13032108</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.38</v>
+        <v>0.45</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
@@ -601,18 +601,18 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>161.5</v>
+        <v>163.2</v>
       </c>
       <c r="D7" t="n">
-        <v>10631099</v>
+        <v>7586311</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.86</v>
+        <v>1.05</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -457,61 +457,61 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0939.HK</t>
+          <t>1810.HK</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>銀行</t>
+          <t>科技</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>9.18</v>
+        <v>28.46</v>
       </c>
       <c r="D2" t="n">
-        <v>192122330</v>
+        <v>142478217</v>
       </c>
       <c r="E2" t="n">
-        <v>0.05</v>
+        <v>2.52</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3690.HK</t>
+          <t>0939.HK</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>科技</t>
+          <t>銀行</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>77.2</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="D3" t="n">
-        <v>91023973</v>
+        <v>138555273</v>
       </c>
       <c r="E3" t="n">
-        <v>-6.65</v>
+        <v>0.38</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1810.HK</t>
+          <t>3690.HK</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -520,18 +520,18 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>27.76</v>
+        <v>78.05</v>
       </c>
       <c r="D4" t="n">
-        <v>81490138</v>
+        <v>30349391</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.22</v>
+        <v>1.1</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
@@ -547,18 +547,18 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>93.59999999999999</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>19581215</v>
+        <v>18686686</v>
       </c>
       <c r="E5" t="n">
-        <v>0.86</v>
+        <v>-1.07</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
@@ -574,18 +574,18 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>442</v>
+        <v>445.4</v>
       </c>
       <c r="D6" t="n">
-        <v>13032108</v>
+        <v>14634642</v>
       </c>
       <c r="E6" t="n">
-        <v>0.45</v>
+        <v>0.77</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
@@ -601,18 +601,18 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>163.2</v>
+        <v>161.7</v>
       </c>
       <c r="D7" t="n">
-        <v>7586311</v>
+        <v>8208758</v>
       </c>
       <c r="E7" t="n">
-        <v>1.05</v>
+        <v>-0.92</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -457,54 +457,46 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1810.HK</t>
+          <t>0939.HK</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>科技</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>28.46</v>
-      </c>
+          <t>銀行</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>142478217</v>
-      </c>
-      <c r="E2" t="n">
-        <v>2.52</v>
-      </c>
+        <v>198830189</v>
+      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0939.HK</t>
+          <t>1810.HK</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>銀行</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>9.220000000000001</v>
-      </c>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>138555273</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0.38</v>
-      </c>
+        <v>145687128</v>
+      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -519,19 +511,15 @@
           <t>科技</t>
         </is>
       </c>
-      <c r="C4" t="n">
-        <v>78.05</v>
-      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>30349391</v>
-      </c>
-      <c r="E4" t="n">
-        <v>1.1</v>
-      </c>
+        <v>27631300</v>
+      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -546,19 +534,15 @@
           <t>新能源</t>
         </is>
       </c>
-      <c r="C5" t="n">
-        <v>92.59999999999999</v>
-      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>18686686</v>
-      </c>
-      <c r="E5" t="n">
-        <v>-1.07</v>
-      </c>
+        <v>18104204</v>
+      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -573,19 +557,15 @@
           <t>科技</t>
         </is>
       </c>
-      <c r="C6" t="n">
-        <v>445.4</v>
-      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>14634642</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0.77</v>
-      </c>
+        <v>11487200</v>
+      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
@@ -600,19 +580,15 @@
           <t>銀行</t>
         </is>
       </c>
-      <c r="C7" t="n">
-        <v>161.7</v>
-      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>8208758</v>
-      </c>
-      <c r="E7" t="n">
-        <v>-0.92</v>
-      </c>
+        <v>4568298</v>
+      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -467,13 +467,13 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>198830189</v>
+        <v>212829907</v>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
     </row>
@@ -490,13 +490,13 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>145687128</v>
+        <v>85332131</v>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
     </row>
@@ -513,59 +513,59 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>27631300</v>
+        <v>33410603</v>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1211.HK</t>
+          <t>0700.HK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>新能源</t>
+          <t>科技</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>18104204</v>
+        <v>27742575</v>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0700.HK</t>
+          <t>1211.HK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>科技</t>
+          <t>新能源</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>11487200</v>
+        <v>10946548</v>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
     </row>
@@ -582,13 +582,13 @@
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>4568298</v>
+        <v>7129035</v>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -465,15 +465,19 @@
           <t>銀行</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="n">
+        <v>9.140000000000001</v>
+      </c>
       <c r="D2" t="n">
-        <v>212829907</v>
-      </c>
-      <c r="E2" t="inlineStr"/>
+        <v>212816907</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.05</v>
+      </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -488,15 +492,19 @@
           <t>科技</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="n">
+        <v>27.82</v>
+      </c>
       <c r="D3" t="n">
-        <v>85332131</v>
-      </c>
-      <c r="E3" t="inlineStr"/>
+        <v>85331331</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1.24</v>
+      </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -511,15 +519,19 @@
           <t>科技</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="n">
+        <v>77.5</v>
+      </c>
       <c r="D4" t="n">
-        <v>33410603</v>
-      </c>
-      <c r="E4" t="inlineStr"/>
+        <v>33410203</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -534,15 +546,19 @@
           <t>科技</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="n">
+        <v>455.2</v>
+      </c>
       <c r="D5" t="n">
-        <v>27742575</v>
-      </c>
-      <c r="E5" t="inlineStr"/>
+        <v>27742475</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1.65</v>
+      </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -557,15 +573,19 @@
           <t>新能源</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="n">
+        <v>91.95</v>
+      </c>
       <c r="D6" t="n">
-        <v>10946548</v>
-      </c>
-      <c r="E6" t="inlineStr"/>
+        <v>10946448</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.77</v>
+      </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -580,15 +600,19 @@
           <t>銀行</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="n">
+        <v>161.4</v>
+      </c>
       <c r="D7" t="n">
-        <v>7129035</v>
-      </c>
-      <c r="E7" t="inlineStr"/>
+        <v>7128635</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-0.25</v>
+      </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -477,7 +477,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -504,7 +504,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -531,7 +531,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -558,7 +558,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -585,7 +585,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -612,7 +612,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -465,26 +465,22 @@
           <t>銀行</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>9.140000000000001</v>
-      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>212816907</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.05</v>
-      </c>
+        <v>526179475</v>
+      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1810.HK</t>
+          <t>3690.HK</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -492,26 +488,22 @@
           <t>科技</t>
         </is>
       </c>
-      <c r="C3" t="n">
-        <v>27.82</v>
-      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>85331331</v>
-      </c>
-      <c r="E3" t="n">
-        <v>1.24</v>
-      </c>
+        <v>91960116</v>
+      </c>
+      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>3690.HK</t>
+          <t>1810.HK</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -519,73 +511,61 @@
           <t>科技</t>
         </is>
       </c>
-      <c r="C4" t="n">
-        <v>77.5</v>
-      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>33410203</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0</v>
-      </c>
+        <v>90331600</v>
+      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0700.HK</t>
+          <t>1211.HK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>科技</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>455.2</v>
-      </c>
+          <t>新能源</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="n">
-        <v>27742475</v>
-      </c>
-      <c r="E5" t="n">
-        <v>1.65</v>
-      </c>
+        <v>43268405</v>
+      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1211.HK</t>
+          <t>0700.HK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>新能源</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>91.95</v>
-      </c>
+          <t>科技</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>10946448</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0.77</v>
-      </c>
+        <v>20154770</v>
+      </c>
+      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
@@ -600,19 +580,15 @@
           <t>銀行</t>
         </is>
       </c>
-      <c r="C7" t="n">
-        <v>161.4</v>
-      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="n">
-        <v>7128635</v>
-      </c>
-      <c r="E7" t="n">
-        <v>-0.25</v>
-      </c>
+        <v>6469275</v>
+      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -465,22 +465,26 @@
           <t>銀行</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="n">
+        <v>9.6</v>
+      </c>
       <c r="D2" t="n">
-        <v>526179475</v>
-      </c>
-      <c r="E2" t="inlineStr"/>
+        <v>308091718</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1.05</v>
+      </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>3690.HK</t>
+          <t>1810.HK</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -488,22 +492,26 @@
           <t>科技</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="n">
+        <v>27.56</v>
+      </c>
       <c r="D3" t="n">
-        <v>91960116</v>
-      </c>
-      <c r="E3" t="inlineStr"/>
+        <v>86643519</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-0.22</v>
+      </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1810.HK</t>
+          <t>3690.HK</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -511,15 +519,19 @@
           <t>科技</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="n">
+        <v>76.65000000000001</v>
+      </c>
       <c r="D4" t="n">
-        <v>90331600</v>
-      </c>
-      <c r="E4" t="inlineStr"/>
+        <v>52934330</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-2.85</v>
+      </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
@@ -534,15 +546,19 @@
           <t>新能源</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="n">
+        <v>88.25</v>
+      </c>
       <c r="D5" t="n">
-        <v>43268405</v>
-      </c>
-      <c r="E5" t="inlineStr"/>
+        <v>31703920</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1.2</v>
+      </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
@@ -557,15 +573,19 @@
           <t>科技</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="n">
+        <v>441.4</v>
+      </c>
       <c r="D6" t="n">
-        <v>20154770</v>
-      </c>
-      <c r="E6" t="inlineStr"/>
+        <v>20290981</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-2.56</v>
+      </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
@@ -580,15 +600,19 @@
           <t>銀行</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="n">
+        <v>160.6</v>
+      </c>
       <c r="D7" t="n">
-        <v>6469275</v>
-      </c>
-      <c r="E7" t="inlineStr"/>
+        <v>11448136</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-0.25</v>
+      </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -466,18 +466,18 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>9.6</v>
+        <v>9.67</v>
       </c>
       <c r="D2" t="n">
-        <v>308091718</v>
+        <v>184557050</v>
       </c>
       <c r="E2" t="n">
-        <v>1.05</v>
+        <v>0.73</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
     </row>
@@ -493,18 +493,18 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>27.56</v>
+        <v>28.06</v>
       </c>
       <c r="D3" t="n">
-        <v>86643519</v>
+        <v>115696798</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.22</v>
+        <v>1.81</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
     </row>
@@ -520,18 +520,18 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>76.65000000000001</v>
+        <v>78.75</v>
       </c>
       <c r="D4" t="n">
-        <v>52934330</v>
+        <v>51240808</v>
       </c>
       <c r="E4" t="n">
-        <v>-2.85</v>
+        <v>2.74</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
     </row>
@@ -547,18 +547,18 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>88.25</v>
+        <v>85.25</v>
       </c>
       <c r="D5" t="n">
-        <v>31703920</v>
+        <v>26685730</v>
       </c>
       <c r="E5" t="n">
-        <v>1.2</v>
+        <v>-3.4</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
     </row>
@@ -574,18 +574,18 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>441.4</v>
+        <v>438.2</v>
       </c>
       <c r="D6" t="n">
-        <v>20290981</v>
+        <v>21341428</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.56</v>
+        <v>-0.72</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
     </row>
@@ -601,18 +601,18 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>160.6</v>
+        <v>162.6</v>
       </c>
       <c r="D7" t="n">
-        <v>11448136</v>
+        <v>9494989</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.25</v>
+        <v>1.25</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -466,18 +466,18 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>9.67</v>
+        <v>9.56</v>
       </c>
       <c r="D2" t="n">
-        <v>184557050</v>
+        <v>245668410</v>
       </c>
       <c r="E2" t="n">
-        <v>0.73</v>
+        <v>-1.09</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
     </row>
@@ -493,18 +493,18 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>28.06</v>
+        <v>27.44</v>
       </c>
       <c r="D3" t="n">
-        <v>115696798</v>
+        <v>117456362</v>
       </c>
       <c r="E3" t="n">
-        <v>1.81</v>
+        <v>-2.21</v>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
     </row>
@@ -520,72 +520,72 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>78.75</v>
+        <v>77.65000000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>51240808</v>
+        <v>31031252</v>
       </c>
       <c r="E4" t="n">
-        <v>2.74</v>
+        <v>-1.4</v>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1211.HK</t>
+          <t>0700.HK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>新能源</t>
+          <t>科技</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>85.25</v>
+        <v>433</v>
       </c>
       <c r="D5" t="n">
-        <v>26685730</v>
+        <v>17387196</v>
       </c>
       <c r="E5" t="n">
-        <v>-3.4</v>
+        <v>-1.19</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0700.HK</t>
+          <t>1211.HK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>科技</t>
+          <t>新能源</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>438.2</v>
+        <v>85.7</v>
       </c>
       <c r="D6" t="n">
-        <v>21341428</v>
+        <v>17224479</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.72</v>
+        <v>0.53</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
     </row>
@@ -601,18 +601,18 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>162.6</v>
+        <v>163.5</v>
       </c>
       <c r="D7" t="n">
-        <v>9494989</v>
+        <v>13990543</v>
       </c>
       <c r="E7" t="n">
-        <v>1.25</v>
+        <v>0.55</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -466,18 +466,18 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>9.56</v>
+        <v>9.76</v>
       </c>
       <c r="D2" t="n">
-        <v>245668410</v>
+        <v>320572344</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.09</v>
+        <v>2.04</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
     </row>
@@ -493,18 +493,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>27.44</v>
+        <v>28.44</v>
       </c>
       <c r="D3" t="n">
-        <v>117456362</v>
+        <v>178924091</v>
       </c>
       <c r="E3" t="n">
-        <v>-2.21</v>
-      </c>
-      <c r="F3" t="inlineStr"/>
+        <v>3.64</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>🔥爆升</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
     </row>
@@ -520,99 +524,103 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>77.65000000000001</v>
+        <v>81.75</v>
       </c>
       <c r="D4" t="n">
-        <v>31031252</v>
+        <v>55906540</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.4</v>
-      </c>
-      <c r="F4" t="inlineStr"/>
+        <v>5.28</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>🔥爆升</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0700.HK</t>
+          <t>0005.HK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>科技</t>
+          <t>銀行</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>433</v>
+        <v>166.7</v>
       </c>
       <c r="D5" t="n">
-        <v>17387196</v>
+        <v>30854916</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.19</v>
+        <v>1.96</v>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1211.HK</t>
+          <t>0700.HK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>新能源</t>
+          <t>科技</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>85.7</v>
+        <v>442.8</v>
       </c>
       <c r="D6" t="n">
-        <v>17224479</v>
+        <v>24026386</v>
       </c>
       <c r="E6" t="n">
-        <v>0.53</v>
+        <v>2.26</v>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0005.HK</t>
+          <t>1211.HK</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>銀行</t>
+          <t>新能源</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>163.5</v>
+        <v>86.15000000000001</v>
       </c>
       <c r="D7" t="n">
-        <v>13990543</v>
+        <v>21025766</v>
       </c>
       <c r="E7" t="n">
-        <v>0.55</v>
+        <v>0.53</v>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -469,7 +469,7 @@
         <v>9.76</v>
       </c>
       <c r="D2" t="n">
-        <v>320572344</v>
+        <v>320533344</v>
       </c>
       <c r="E2" t="n">
         <v>2.04</v>
@@ -477,7 +477,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
@@ -496,7 +496,7 @@
         <v>28.44</v>
       </c>
       <c r="D3" t="n">
-        <v>178924091</v>
+        <v>178857691</v>
       </c>
       <c r="E3" t="n">
         <v>3.64</v>
@@ -508,7 +508,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
@@ -527,7 +527,7 @@
         <v>81.75</v>
       </c>
       <c r="D4" t="n">
-        <v>55906540</v>
+        <v>55906440</v>
       </c>
       <c r="E4" t="n">
         <v>5.28</v>
@@ -539,7 +539,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
@@ -558,7 +558,7 @@
         <v>166.7</v>
       </c>
       <c r="D5" t="n">
-        <v>30854916</v>
+        <v>30851316</v>
       </c>
       <c r="E5" t="n">
         <v>1.96</v>
@@ -566,7 +566,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
@@ -585,7 +585,7 @@
         <v>442.8</v>
       </c>
       <c r="D6" t="n">
-        <v>24026386</v>
+        <v>24025286</v>
       </c>
       <c r="E6" t="n">
         <v>2.26</v>
@@ -593,7 +593,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
@@ -612,7 +612,7 @@
         <v>86.15000000000001</v>
       </c>
       <c r="D7" t="n">
-        <v>21025766</v>
+        <v>20988366</v>
       </c>
       <c r="E7" t="n">
         <v>0.53</v>
@@ -620,7 +620,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>

--- a/data/output.xlsx
+++ b/data/output.xlsx
@@ -477,7 +477,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -539,7 +539,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -566,7 +566,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -593,7 +593,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -620,7 +620,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
